--- a/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
@@ -1,24 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1F824C-2EBB-4943-82D8-8D19382EC710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CB5B99-5C5B-4D03-B141-BF7A482A7A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.全体概要" sheetId="13" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.全体概要'!$A$1:$AI$93</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,11 +37,25 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>XXXプロジェクト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>工程</t>
     <rPh sb="0" eb="2">
       <t>コウテイ</t>
     </rPh>
     <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>要件定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>作成</t>
@@ -57,6 +69,9 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>アプリケーション方式設計書</t>
+  </si>
+  <si>
     <t>変更</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -66,19 +81,6 @@
   <si>
     <t>確認</t>
     <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>アプリケーション方式設計書</t>
-  </si>
-  <si>
-    <t>理由</t>
-    <rPh sb="0" eb="2">
-      <t>リユウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アプリケーション・アーキテクチャ</t>
   </si>
   <si>
     <t>2.</t>
@@ -105,6 +107,25 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>本システムで稼働するアプリケーションの全体図を以下に記載する。</t>
+  </si>
+  <si>
+    <t>※WEBサーバー・Applicationサーバーは複数台で構成し、前段にロードバランサーを配置する。</t>
+    <rPh sb="25" eb="28">
+      <t>フクスウダイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゼンダン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>ソフトウェア構成</t>
     <rPh sb="6" eb="8">
       <t>コウセイ</t>
@@ -115,24 +136,10 @@
     <t>本アプリケーションのソフトウェア構成は以下の通り。</t>
   </si>
   <si>
-    <t>本システムのアプリケーション・アーキテクチャは、Nablarch Application Frameworkをベースとする。</t>
+    <t>アプリケーション・アーキテクチャ</t>
   </si>
   <si>
-    <t>本システムで稼働するアプリケーションの全体図を以下に記載する。</t>
-  </si>
-  <si>
-    <t>XXXプロジェクト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>要件定義</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <t>本システムのアプリケーション・アーキテクチャは、Nablarch Application Frameworkをベースとする。</t>
   </si>
   <si>
     <t>Nablarch が提供するアプリケーション・アーキテクチャについては、以下のNablarch解説書を参照。</t>
@@ -148,6 +155,10 @@
     <rPh sb="51" eb="53">
       <t>サンショウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/nablarch/big_picture.html</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -168,18 +179,6 @@
     <rPh sb="28" eb="29">
       <t>トオ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Java</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ソフトウェア</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Nablarch</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -220,10 +219,29 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>ソフトウェア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>種類およびバージョン</t>
     <rPh sb="0" eb="2">
       <t>シュルイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>理由</t>
+    <rPh sb="0" eb="2">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Java</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RedHat OpenJDK 21</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -240,30 +258,6 @@
     <rPh sb="38" eb="40">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>※WEBサーバー・Applicationサーバーは複数台で構成し、前段にロードバランサーを配置する。</t>
-    <rPh sb="25" eb="28">
-      <t>フクスウダイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ゼンダン</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ハイチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/nablarch/big_picture.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>RedHat OpenJDK 21</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -292,6 +286,14 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>Nablarch</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>6u2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>2024年9月現在最新バージョンである6u2を選択する。</t>
     <rPh sb="4" eb="5">
       <t>ネン</t>
@@ -308,10 +310,6 @@
     <rPh sb="23" eb="25">
       <t>センタク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>6u2</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -554,47 +552,47 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -636,9 +634,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -675,19 +670,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -708,23 +703,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -744,7 +730,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -785,17 +771,17 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>250975</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="192" name="グループ化 191">
+        <xdr:cNvPr id="171" name="グループ化 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C0000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E17E99-7FE1-9C30-829C-4EEDC7FBD431}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -804,9 +790,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="828675" y="7229475"/>
-          <a:ext cx="8610600" cy="3476626"/>
-          <a:chOff x="63212" y="3335473"/>
-          <a:chExt cx="8773832" cy="3306750"/>
+          <a:ext cx="7985275" cy="3476626"/>
+          <a:chOff x="828675" y="7229475"/>
+          <a:chExt cx="7985275" cy="3476626"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -822,8 +808,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2540583" y="6280273"/>
-            <a:ext cx="6277203" cy="361950"/>
+            <a:off x="2650356" y="10325557"/>
+            <a:ext cx="6163594" cy="380544"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -966,8 +952,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4187504" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="4266637" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1113,8 +1099,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5348895" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="5406421" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1262,8 +1248,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6501023" y="6367469"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="6537114" y="10417232"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1432,8 +1418,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2972631" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="3074366" y="10417231"/>
+            <a:ext cx="1063082" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1582,8 +1568,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124077" y="5733256"/>
-            <a:ext cx="8624387" cy="251511"/>
+            <a:off x="888408" y="9750438"/>
+            <a:ext cx="7826967" cy="264432"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1736,8 +1722,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7709050" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="7725842" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1894,8 +1880,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124076" y="5496803"/>
-            <a:ext cx="2343119" cy="218680"/>
+            <a:off x="888408" y="9501838"/>
+            <a:ext cx="1505543" cy="229914"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2091,8 +2077,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124077" y="4598329"/>
-            <a:ext cx="728643" cy="898475"/>
+            <a:off x="888408" y="8557207"/>
+            <a:ext cx="470492" cy="944632"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2240,8 +2226,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="859586" y="4598072"/>
-            <a:ext cx="822119" cy="901012"/>
+            <a:off x="1359409" y="8556937"/>
+            <a:ext cx="529632" cy="947299"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2404,8 +2390,667 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1683419" y="4598329"/>
-            <a:ext cx="776817" cy="898473"/>
+            <a:off x="1891689" y="8557207"/>
+            <a:ext cx="500442" cy="944630"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Apache</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="205" name="正方形/長方形 204">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CD000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2574925" y="9501837"/>
+            <a:ext cx="4269018" cy="248600"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>仮想</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>OS</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>（</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>RHEL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>）</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="206" name="正方形/長方形 205">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2581997" y="8557207"/>
+            <a:ext cx="475528" cy="944632"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>vSphere Data Protection</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="207" name="正方形/長方形 206">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CF000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3059074" y="8556938"/>
+            <a:ext cx="446126" cy="947298"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>ServerProtect</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>for Linux</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="208" name="正方形/長方形 207">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D0000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4140200" y="8829676"/>
+            <a:ext cx="1788806" cy="208800"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2535,17 +3180,17 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>Apache</a:t>
+              <a:t>Tomcat</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="205" name="正方形/長方形 204">
+          <xdr:cNvPr id="209" name="正方形/長方形 208">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CD000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D1000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2553,8 +3198,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2771799" y="5496802"/>
-            <a:ext cx="3420713" cy="236453"/>
+            <a:off x="4140200" y="9047391"/>
+            <a:ext cx="2703744" cy="456844"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2563,13 +3208,13 @@
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:lnRef>
           <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:fillRef>
           <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:effectRef>
           <a:fontRef idx="minor">
             <a:schemeClr val="dk1"/>
@@ -2675,7 +3320,7 @@
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
                 <a:solidFill>
                   <a:schemeClr val="tx2">
                     <a:lumMod val="75000"/>
@@ -2684,65 +3329,17 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>仮想</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>OS</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>（</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>RHEL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>）</a:t>
+              <a:t>JDK(OpenJDK 21)</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="206" name="正方形/長方形 205">
+          <xdr:cNvPr id="210" name="正方形/長方形 209">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2750,8 +3347,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2771801" y="4598329"/>
-            <a:ext cx="484543" cy="898475"/>
+            <a:off x="3501453" y="8557857"/>
+            <a:ext cx="279972" cy="938193"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2881,617 +3478,6 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>vSphere Data Protection</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="207" name="正方形/長方形 206">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CF000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3257922" y="4598073"/>
-            <a:ext cx="454583" cy="901011"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ServerProtect</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>for Linux</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="208" name="正方形/長方形 207">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D0000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4350091" y="4857484"/>
-            <a:ext cx="910140" cy="198598"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>Tomcat</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="209" name="正方形/長方形 208">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D1000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4347149" y="5064561"/>
-            <a:ext cx="1845364" cy="434522"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>JDK(OpenJDK 21)</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="210" name="正方形/長方形 209">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3708687" y="4598947"/>
-            <a:ext cx="285279" cy="892351"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
               <a:t>HULFT</a:t>
             </a:r>
           </a:p>
@@ -3510,8 +3496,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4350093" y="4598638"/>
-            <a:ext cx="910138" cy="252375"/>
+            <a:off x="5035801" y="8557532"/>
+            <a:ext cx="893205" cy="265340"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3664,8 +3650,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4338271" y="3919169"/>
-            <a:ext cx="908230" cy="663735"/>
+            <a:off x="5024199" y="7843157"/>
+            <a:ext cx="891333" cy="697833"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3854,8 +3840,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6477353" y="5516989"/>
-            <a:ext cx="2271111" cy="218680"/>
+            <a:off x="7123485" y="9523061"/>
+            <a:ext cx="1591890" cy="229914"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4051,8 +4037,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6477354" y="4586591"/>
-            <a:ext cx="739483" cy="930401"/>
+            <a:off x="7134224" y="8544866"/>
+            <a:ext cx="514961" cy="978198"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4200,8 +4186,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7223703" y="4586866"/>
-            <a:ext cx="699976" cy="932403"/>
+            <a:off x="7660807" y="8545155"/>
+            <a:ext cx="485220" cy="980303"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4364,8 +4350,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7930826" y="4586563"/>
-            <a:ext cx="818412" cy="930669"/>
+            <a:off x="8148220" y="8544837"/>
+            <a:ext cx="569883" cy="978480"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4387,7 +4373,7 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
           <a:lstStyle>
             <a:defPPr>
               <a:defRPr lang="ja-JP"/>
@@ -4513,8 +4499,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2699792" y="3345343"/>
-            <a:ext cx="3600400" cy="2747952"/>
+            <a:off x="2530475" y="7239852"/>
+            <a:ext cx="4419145" cy="2889121"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4687,8 +4673,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4003672" y="4598947"/>
-            <a:ext cx="336611" cy="892351"/>
+            <a:off x="3794125" y="8557857"/>
+            <a:ext cx="330349" cy="938193"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4836,8 +4822,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6372199" y="3335473"/>
-            <a:ext cx="2464845" cy="2757823"/>
+            <a:off x="7020288" y="7229475"/>
+            <a:ext cx="1783988" cy="2899499"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5010,8 +4996,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="63212" y="3345343"/>
-            <a:ext cx="2464845" cy="2747952"/>
+            <a:off x="828675" y="7239852"/>
+            <a:ext cx="1622425" cy="2889121"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5184,8 +5170,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5253366" y="4592167"/>
-            <a:ext cx="940545" cy="465921"/>
+            <a:off x="5922269" y="8550729"/>
+            <a:ext cx="923047" cy="489857"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5338,8 +5324,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5246501" y="3919169"/>
-            <a:ext cx="954274" cy="663735"/>
+            <a:off x="5915532" y="7843157"/>
+            <a:ext cx="936520" cy="697833"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5535,102 +5521,431 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="169" name="正方形/長方形 168">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B651FC0-E278-80C7-E48C-D1EA58E201E7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4140451" y="8557532"/>
+            <a:ext cx="890030" cy="265340"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent2"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent2"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent2"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Nablarch</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="170" name="正方形/長方形 169">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F254B2E8-EFAF-E6D0-6C4E-613EA3F888AD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4141549" y="7843157"/>
+            <a:ext cx="888158" cy="697833"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>業務</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>アプリケーション</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(REST API)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="162" name="正方形/長方形 161">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="20043632">
+            <a:off x="2784489" y="8055504"/>
+            <a:ext cx="4773206" cy="2445229"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>SAMPLE</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>98441</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>92606</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>175822</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>108960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="162" name="正方形/長方形 161">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="20043632">
-          <a:off x="3413141" y="7636406"/>
-          <a:ext cx="4773206" cy="2445229"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>SAMPLE</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:colOff>19783</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>81777</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>60993</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="グループ化 1">
+        <xdr:cNvPr id="87" name="グループ化 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95EA71B2-7203-B593-A30D-B714737D7062}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5638,18 +5953,341 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="361950" y="1339077"/>
-          <a:ext cx="9036050" cy="4944248"/>
-          <a:chOff x="339725" y="1313677"/>
-          <a:chExt cx="8324850" cy="5182373"/>
+          <a:off x="296008" y="1339077"/>
+          <a:ext cx="9101992" cy="4836966"/>
+          <a:chOff x="295680" y="1356156"/>
+          <a:chExt cx="9091153" cy="4892803"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA608710-AA6F-4D02-B913-2DF03E93065E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="2423622" y="1513020"/>
+            <a:ext cx="5672135" cy="3444475"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFCC"/>
+          </a:solidFill>
+          <a:ln w="31750">
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>XXX</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>システム</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4ACDA9-6EE9-48F6-A3F1-0F4D6190EA75}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="4106865" y="1854180"/>
+            <a:ext cx="1846084" cy="2947228"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Application</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>サーバ</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="137" name="グループ化 136">
+          <xdr:cNvPr id="5" name="グループ化 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000089000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3022DEAD-879D-4481-93D4-B0B50524E849}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5657,18 +6295,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="5320506" y="4963317"/>
-            <a:ext cx="288925" cy="811213"/>
+            <a:off x="5778685" y="4914667"/>
+            <a:ext cx="278933" cy="879203"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="140" name="円/楕円 139">
+            <xdr:cNvPr id="6" name="円/楕円 139">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A94CAE69-A36E-9EEF-80F8-2A9EAC69722E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5717,16 +6355,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="141" name="直線コネクタ 140">
+            <xdr:cNvPr id="7" name="直線コネクタ 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DCAB10-44A4-E652-87ED-1928760CA3A5}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="140" idx="1"/>
-              <a:endCxn id="140" idx="5"/>
+              <a:stCxn id="6" idx="1"/>
+              <a:endCxn id="6" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5756,16 +6394,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="142" name="直線コネクタ 141">
+            <xdr:cNvPr id="8" name="直線コネクタ 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68F3499-16E9-E2E0-4155-5E6D03953CEB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="140" idx="7"/>
-              <a:endCxn id="140" idx="3"/>
+              <a:stCxn id="6" idx="7"/>
+              <a:endCxn id="6" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5796,10 +6434,10 @@
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="110" name="グループ化 109">
+          <xdr:cNvPr id="9" name="グループ化 8">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D291FC0-3000-4F6B-A209-671F8956A55F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5807,18 +6445,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1628775" y="3235324"/>
-            <a:ext cx="273050" cy="727076"/>
+            <a:off x="1759154" y="2980436"/>
+            <a:ext cx="296049" cy="701879"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="111" name="円/楕円 110">
+            <xdr:cNvPr id="10" name="円/楕円 110">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{978C39C3-A67C-2356-E087-03ECC87F0280}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5867,16 +6505,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="115" name="直線コネクタ 114">
+            <xdr:cNvPr id="11" name="直線コネクタ 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D6A886-097E-27C5-EC6D-A1B307233B4D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="111" idx="1"/>
-              <a:endCxn id="111" idx="5"/>
+              <a:stCxn id="10" idx="1"/>
+              <a:endCxn id="10" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5906,16 +6544,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="116" name="直線コネクタ 115">
+            <xdr:cNvPr id="13" name="直線コネクタ 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572E2F6F-0D57-E01F-535C-D113D5E00AA0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="111" idx="7"/>
-              <a:endCxn id="111" idx="3"/>
+              <a:stCxn id="10" idx="7"/>
+              <a:endCxn id="10" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5946,10 +6584,10 @@
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="19" name="グループ化 18">
+          <xdr:cNvPr id="15" name="グループ化 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28DB3A29-8298-4285-B1D3-2D47F78D4427}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5957,18 +6595,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1628775" y="1924050"/>
-            <a:ext cx="273050" cy="977900"/>
+            <a:off x="1759154" y="2055581"/>
+            <a:ext cx="296049" cy="759221"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="円/楕円 11">
+            <xdr:cNvPr id="16" name="円/楕円 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FECAEB3C-5884-E3D7-A3C9-9C775B3429F0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6017,16 +6655,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="14" name="直線コネクタ 13">
+            <xdr:cNvPr id="17" name="直線コネクタ 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5988C8B3-1D45-B160-F099-1E2759E30D44}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="12" idx="1"/>
-              <a:endCxn id="12" idx="5"/>
+              <a:stCxn id="16" idx="1"/>
+              <a:endCxn id="16" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -6056,16 +6694,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="109" name="直線コネクタ 108">
+            <xdr:cNvPr id="18" name="直線コネクタ 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C02A634A-BBC2-5CE9-37DF-3C951DA9D8D7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="12" idx="7"/>
-              <a:endCxn id="12" idx="3"/>
+              <a:stCxn id="16" idx="7"/>
+              <a:endCxn id="16" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -6096,10 +6734,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="85" name="Rectangle 37">
+          <xdr:cNvPr id="22" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03036546-3D11-4F19-904C-44CB893CE0C8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6109,160 +6747,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2241550" y="1476375"/>
-            <a:ext cx="5232053" cy="3387725"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFFCC"/>
-          </a:solidFill>
-          <a:ln w="31750">
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>XXX</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>システム</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="86" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="8163799" y="1466850"/>
-            <a:ext cx="500776" cy="3897840"/>
+            <a:off x="8843932" y="1503934"/>
+            <a:ext cx="542901" cy="3761436"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6395,10 +6881,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="87" name="Rectangle 37">
+          <xdr:cNvPr id="23" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCC3881-A349-48BB-8650-E411667E6D2F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6408,8 +6894,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2406145" y="1838326"/>
-            <a:ext cx="828638" cy="1863724"/>
+            <a:off x="2601950" y="1863266"/>
+            <a:ext cx="898444" cy="2773110"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6566,10 +7052,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="88" name="Rectangle 37">
+          <xdr:cNvPr id="24" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C172EBC5-7274-4FE8-91B3-931A8AB32736}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6579,8 +7065,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="339725" y="2102668"/>
-            <a:ext cx="1149349" cy="240482"/>
+            <a:off x="295680" y="2621904"/>
+            <a:ext cx="1246225" cy="234739"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6716,28 +7202,15 @@
               </a:rPr>
               <a:t>一般ユーザグループ</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>1</a:t>
-            </a:r>
-            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="96" name="Rectangle 37">
+          <xdr:cNvPr id="25" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030735C4-9295-4139-A2BF-3685BFD3EF53}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6747,8 +7220,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5705259" y="5593996"/>
-            <a:ext cx="1400391" cy="425804"/>
+            <a:off x="5997996" y="5428632"/>
+            <a:ext cx="1518057" cy="408659"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6897,10 +7370,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="97" name="Rectangle 37">
+          <xdr:cNvPr id="26" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE7A7956-8BF9-43FA-BF96-D7DF9B0F7B35}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6910,8 +7383,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5735127" y="1796538"/>
-            <a:ext cx="1384252" cy="263530"/>
+            <a:off x="6026628" y="1821757"/>
+            <a:ext cx="1869733" cy="254706"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7068,10 +7541,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="101" name="フローチャート : 磁気ディスク 100">
+          <xdr:cNvPr id="32" name="正方形/長方形 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C25F9F6-86A9-49DD-8368-3AD75EDDB02A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7079,850 +7552,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5598997" y="2675698"/>
-            <a:ext cx="1802626" cy="1577690"/>
-          </a:xfrm>
-          <a:prstGeom prst="flowChartMagneticDisk">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="CC99FF"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="9900CC"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>　</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>     サーバ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="102" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="3794125" y="1828801"/>
-            <a:ext cx="1702902" cy="2895599"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="accent6">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>Application</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>サーバ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="103" name="正方形/長方形 102">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5702592" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>１</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="104" name="正方形/長方形 103">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6234426" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>２</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="105" name="正方形/長方形 104">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6797140" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>３</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="106" name="正方形/長方形 105">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2484559" y="2174822"/>
-            <a:ext cx="671810" cy="336730"/>
+            <a:off x="2687063" y="2187585"/>
+            <a:ext cx="728218" cy="325240"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8059,10 +7690,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="107" name="正方形/長方形 106">
+          <xdr:cNvPr id="34" name="正方形/長方形 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C11DF84-AE30-4CDE-B061-50F9898BE506}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8070,8 +7701,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2484559" y="2603598"/>
-            <a:ext cx="671810" cy="336730"/>
+            <a:off x="2687063" y="2740164"/>
+            <a:ext cx="728218" cy="324639"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8208,10 +7839,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="108" name="正方形/長方形 107">
+          <xdr:cNvPr id="35" name="正方形/長方形 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7015A2C9-7DF8-431C-A80F-DC03CC2EFC1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8219,157 +7850,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2484559" y="3038960"/>
-            <a:ext cx="671810" cy="336730"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>WEB3</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="112" name="正方形/長方形 111">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3971436" y="2180706"/>
-            <a:ext cx="1386024" cy="336730"/>
+            <a:off x="4298995" y="2193199"/>
+            <a:ext cx="1502463" cy="325240"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8502,7 +7984,7 @@
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>WEB1</a:t>
+              <a:t>WEB</a:t>
             </a:r>
             <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
@@ -8514,10 +7996,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="113" name="正方形/長方形 112">
+          <xdr:cNvPr id="37" name="正方形/長方形 36">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D1C70F-7607-4906-805E-2499787D4B0E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8525,165 +8007,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3968218" y="2590885"/>
-            <a:ext cx="1389241" cy="336730"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>会員</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>WEB2</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="114" name="正方形/長方形 113">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3968218" y="3026245"/>
-            <a:ext cx="1389241" cy="336730"/>
+            <a:off x="4295502" y="2728033"/>
+            <a:ext cx="1505955" cy="324639"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8828,10 +8153,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="118" name="正方形/長方形 117">
+          <xdr:cNvPr id="38" name="正方形/長方形 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D14AECC-E9E0-4BAE-9AF3-0B03B5F51DB6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8839,8 +8164,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3971926" y="4288570"/>
-            <a:ext cx="1333587" cy="311396"/>
+            <a:off x="4281323" y="4321895"/>
+            <a:ext cx="1511703" cy="300373"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8970,133 +8295,12 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="119" name="カギ線コネクタ 118">
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="42" name="正方形/長方形 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="118" idx="3"/>
-            <a:endCxn id="105" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="5305512" y="4116072"/>
-            <a:ext cx="1745951" cy="328196"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="120" name="直線コネクタ 119">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="103" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5956916" y="4116072"/>
-            <a:ext cx="1" cy="314656"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:headEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="121" name="直線コネクタ 120">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="104" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6488750" y="4116072"/>
-            <a:ext cx="1" cy="307509"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:headEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="123" name="正方形/長方形 122">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CB45709-F3E0-489E-A4D5-205A692230B5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9104,8 +8308,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2493381" y="3020247"/>
-            <a:ext cx="2872901" cy="366371"/>
+            <a:off x="2696639" y="2722311"/>
+            <a:ext cx="3114395" cy="361591"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9238,10 +8442,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="125" name="正方形/長方形 124">
+          <xdr:cNvPr id="44" name="正方形/長方形 43">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49F8FC2D-E023-489D-90E5-2AE22264B1C2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9249,155 +8453,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2498987" y="2596248"/>
-            <a:ext cx="2872901" cy="366371"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="38100">
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="127" name="正方形/長方形 126">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2483450" y="2172533"/>
-            <a:ext cx="2896720" cy="370922"/>
+            <a:off x="2685860" y="2185401"/>
+            <a:ext cx="3140249" cy="366448"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9530,71 +8587,28 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="128" name="カギ線コネクタ 127">
+          <xdr:cNvPr id="46" name="カギ線コネクタ 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36F2E2BD-0297-4F68-A03D-ACBADFE2D190}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:stCxn id="113" idx="3"/>
-            <a:endCxn id="104" idx="0"/>
+            <a:cxnSpLocks/>
+            <a:stCxn id="37" idx="3"/>
+            <a:endCxn id="27" idx="2"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5357459" y="2759251"/>
-            <a:ext cx="1131291" cy="712755"/>
+            <a:off x="5801457" y="2890353"/>
+            <a:ext cx="871298" cy="322579"/>
           </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="131" name="カギ線コネクタ 130">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="114" idx="3"/>
-            <a:endCxn id="105" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5357459" y="3194610"/>
-            <a:ext cx="1694005" cy="277396"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+            </a:avLst>
           </a:prstGeom>
           <a:ln>
             <a:solidFill>
@@ -9620,10 +8634,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="133" name="Rectangle 37">
+          <xdr:cNvPr id="47" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75F4A3F8-5B61-4630-977E-001643E152C3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9633,8 +8647,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4713604" y="6087908"/>
-            <a:ext cx="3550293" cy="408142"/>
+            <a:off x="5103583" y="5857151"/>
+            <a:ext cx="3849000" cy="391808"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9767,10 +8781,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="134" name="Rectangle 37">
+          <xdr:cNvPr id="48" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000086000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F4D7935-FE5E-4C8A-B50F-46F80CC81358}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9780,8 +8794,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4117637" y="5589476"/>
-            <a:ext cx="1312619" cy="401749"/>
+            <a:off x="4119438" y="5443149"/>
+            <a:ext cx="1870630" cy="388216"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9957,22 +8971,23 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="135" name="カギ線コネクタ 134">
+          <xdr:cNvPr id="49" name="カギ線コネクタ 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57A5271-5E5C-4113-8252-286F96F90F0E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:stCxn id="112" idx="3"/>
-            <a:endCxn id="103" idx="0"/>
+            <a:cxnSpLocks/>
+            <a:stCxn id="35" idx="3"/>
+            <a:endCxn id="27" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5357460" y="2349071"/>
-            <a:ext cx="599456" cy="1122935"/>
+            <a:off x="5801458" y="2355819"/>
+            <a:ext cx="1326794" cy="417269"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -10001,10 +9016,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="138" name="右矢印 137">
+          <xdr:cNvPr id="50" name="右矢印 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5839805-50E1-49A5-B03B-8B11FCD9D1B4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10012,8 +9027,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="3950322">
-            <a:off x="4609023" y="5322693"/>
-            <a:ext cx="1452817" cy="143007"/>
+            <a:off x="5094495" y="5222401"/>
+            <a:ext cx="1119530" cy="154722"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10156,10 +9171,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="146" name="Rectangle 37">
+          <xdr:cNvPr id="51" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED17BFF-1754-47E8-8F27-39145D3FBE8A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10169,8 +9184,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1316877" y="6087907"/>
-            <a:ext cx="2313138" cy="408142"/>
+            <a:off x="1420940" y="5857150"/>
+            <a:ext cx="2507796" cy="391808"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10303,10 +9318,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="147" name="Rectangle 37">
+          <xdr:cNvPr id="52" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93D2C61-DAF2-4DC1-A87E-A4A0B06576F0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10316,8 +9331,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1422400" y="5568177"/>
-            <a:ext cx="1190261" cy="369073"/>
+            <a:off x="1697074" y="5325293"/>
+            <a:ext cx="1290633" cy="355399"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10466,10 +9481,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="150" name="Rectangle 37">
+          <xdr:cNvPr id="53" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6FF2C5F-35B4-4353-9255-0844B41B2646}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10479,8 +9494,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2822575" y="5718958"/>
-            <a:ext cx="1309446" cy="348467"/>
+            <a:off x="3233853" y="5712848"/>
+            <a:ext cx="1419843" cy="337383"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10629,10 +9644,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="160" name="右矢印 159">
+          <xdr:cNvPr id="54" name="右矢印 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16CBE5C0-95F5-4756-B9CA-56A72D40B8FA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10640,8 +9655,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="14796441">
-            <a:off x="4809761" y="5266642"/>
-            <a:ext cx="1415738" cy="172607"/>
+            <a:off x="5278793" y="5160908"/>
+            <a:ext cx="1148895" cy="187527"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10784,69 +9799,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="161" name="正方形/長方形 160">
+          <xdr:cNvPr id="56" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A1000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20043632">
-            <a:off x="2723540" y="2610380"/>
-            <a:ext cx="4392659" cy="1832455"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent6"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent6"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent6"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>SAMPLE</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="163" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A3000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A11520-2A1D-408F-B604-EBDCBC2B3CF3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10856,8 +9812,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1155152" y="1313677"/>
-            <a:ext cx="1130484" cy="470673"/>
+            <a:off x="1245726" y="1356156"/>
+            <a:ext cx="1225748" cy="453973"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11014,21 +9970,22 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="82" name="カギ線コネクタ 81">
+          <xdr:cNvPr id="57" name="カギ線コネクタ 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{019FE981-1798-40D0-B71D-7F37127A9BE6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:endCxn id="127" idx="1"/>
+            <a:stCxn id="80" idx="3"/>
+            <a:endCxn id="44" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1148939" y="1871546"/>
-            <a:ext cx="1334511" cy="484861"/>
+          <a:xfrm flipV="1">
+            <a:off x="1142215" y="2368625"/>
+            <a:ext cx="1543645" cy="49924"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -11057,68 +10014,21 @@
       </xdr:cxnSp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="89" name="カギ線コネクタ 88">
+          <xdr:cNvPr id="59" name="カギ線コネクタ 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA83CD41-C7AC-42F7-A548-6376105D6CB0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:endCxn id="107" idx="1"/>
+            <a:endCxn id="42" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1196564" y="2770376"/>
-            <a:ext cx="1287995" cy="2870"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="91" name="カギ線コネクタ 90">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:endCxn id="123" idx="1"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1148939" y="3201845"/>
-            <a:ext cx="1344442" cy="523901"/>
+            <a:off x="1238982" y="2901275"/>
+            <a:ext cx="1457657" cy="500687"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -11147,10 +10057,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="テキスト ボックス 19">
+          <xdr:cNvPr id="60" name="テキスト ボックス 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DE58D3D-A137-4DD1-8E57-0A07A9ECDC45}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11158,8 +10068,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1431926" y="2387599"/>
-            <a:ext cx="714374" cy="177800"/>
+            <a:off x="1545817" y="2529418"/>
+            <a:ext cx="774418" cy="171271"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11205,10 +10115,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="117" name="テキスト ボックス 116">
+          <xdr:cNvPr id="61" name="テキスト ボックス 60">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CA41892-879D-41E3-B498-1339DA622C6D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11216,8 +10126,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1479550" y="3711574"/>
-            <a:ext cx="571500" cy="149226"/>
+            <a:off x="1597509" y="3439730"/>
+            <a:ext cx="619338" cy="144011"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11263,10 +10173,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="122" name="Rectangle 37">
+          <xdr:cNvPr id="63" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D25285-BAF2-4920-A0CA-FEF27D886B95}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11276,8 +10186,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="387350" y="3007543"/>
-            <a:ext cx="1136649" cy="237307"/>
+            <a:off x="362027" y="3751806"/>
+            <a:ext cx="1345838" cy="228045"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11411,174 +10321,6 @@
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>一般ユーザグループ</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>2</a:t>
-            </a:r>
-            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="124" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="387350" y="3975918"/>
-            <a:ext cx="1241425" cy="237307"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
               <a:t>管理者ユーザグループ</a:t>
             </a:r>
           </a:p>
@@ -11586,10 +10328,10 @@
       </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="126" name="グループ化 125">
+          <xdr:cNvPr id="64" name="グループ化 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8B8E4FF-6D30-49E1-9547-F2E1B09EF1CA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11597,18 +10339,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="7686675" y="1939924"/>
-            <a:ext cx="273050" cy="727076"/>
+            <a:off x="8326704" y="1960197"/>
+            <a:ext cx="296048" cy="701879"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="129" name="円/楕円 128">
+            <xdr:cNvPr id="65" name="円/楕円 128">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6466ED1-F3AB-76C1-35D3-55045E12BFB4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11657,16 +10399,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="130" name="直線コネクタ 129">
+            <xdr:cNvPr id="66" name="直線コネクタ 65">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1B94BE7-97A4-8333-3988-8A2DEFF2A221}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="129" idx="1"/>
-              <a:endCxn id="129" idx="5"/>
+              <a:stCxn id="65" idx="1"/>
+              <a:endCxn id="65" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -11696,16 +10438,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="132" name="直線コネクタ 131">
+            <xdr:cNvPr id="67" name="直線コネクタ 66">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E24BAC7-97F7-E99F-3E80-2F3809B0BD21}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="129" idx="7"/>
-              <a:endCxn id="129" idx="3"/>
+              <a:stCxn id="65" idx="7"/>
+              <a:endCxn id="65" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -11736,10 +10478,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="136" name="テキスト ボックス 135">
+          <xdr:cNvPr id="68" name="テキスト ボックス 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000088000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38C594BC-BF05-4ADA-B0F9-8720B3D32C0C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11747,8 +10489,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7537450" y="2416174"/>
-            <a:ext cx="587375" cy="149226"/>
+            <a:off x="8165059" y="2419490"/>
+            <a:ext cx="636898" cy="144011"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11794,10 +10536,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="139" name="右矢印 138">
+          <xdr:cNvPr id="69" name="右矢印 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11FFCEC8-5787-4763-BE64-2EDE891F776B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11805,8 +10547,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5437948" y="2016126"/>
-            <a:ext cx="2683702" cy="230060"/>
+            <a:off x="5888822" y="2034540"/>
+            <a:ext cx="2909688" cy="221131"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -11945,10 +10687,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="143" name="テキスト ボックス 142">
+          <xdr:cNvPr id="70" name="テキスト ボックス 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362E1E1C-B77B-49B1-96D1-C2C02FB06230}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11956,8 +10698,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5683250" y="5181599"/>
-            <a:ext cx="593725" cy="149226"/>
+            <a:off x="6154753" y="5176417"/>
+            <a:ext cx="643791" cy="142369"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12003,10 +10745,10 @@
       </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="144" name="グループ化 143">
+          <xdr:cNvPr id="71" name="グループ化 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80835035-7B65-417B-84CD-024951B5177C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12014,18 +10756,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="3049588" y="4695823"/>
-            <a:ext cx="288925" cy="1289052"/>
+            <a:off x="3316716" y="4628405"/>
+            <a:ext cx="278933" cy="1397206"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="145" name="円/楕円 144">
+            <xdr:cNvPr id="72" name="円/楕円 144">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{597E2665-565B-7AE6-EC25-ED6C93F31BD1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12074,16 +10816,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="151" name="直線コネクタ 150">
+            <xdr:cNvPr id="73" name="直線コネクタ 72">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000097000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5D15FF-6461-4AAB-765E-D10C04E28C61}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="145" idx="1"/>
-              <a:endCxn id="145" idx="5"/>
+              <a:stCxn id="72" idx="1"/>
+              <a:endCxn id="72" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -12113,16 +10855,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="152" name="直線コネクタ 151">
+            <xdr:cNvPr id="74" name="直線コネクタ 73">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000098000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15B3A1A1-C546-938E-D1C1-19C6C9271C46}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="145" idx="7"/>
-              <a:endCxn id="145" idx="3"/>
+              <a:stCxn id="72" idx="7"/>
+              <a:endCxn id="72" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -12153,10 +10895,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="153" name="テキスト ボックス 152">
+          <xdr:cNvPr id="75" name="テキスト ボックス 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE805A00-B58D-44DC-9E5C-8FFEA627E4BC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12164,8 +10906,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2279650" y="5079999"/>
-            <a:ext cx="571500" cy="149226"/>
+            <a:off x="2464978" y="5075337"/>
+            <a:ext cx="619339" cy="144010"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12211,10 +10953,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="149" name="右矢印 148">
+          <xdr:cNvPr id="76" name="右矢印 148">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEC7A79-5E1A-4D58-B1CA-BC54B21B4FF2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12222,8 +10964,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="8439195">
-            <a:off x="2032898" y="5251880"/>
-            <a:ext cx="2088890" cy="175670"/>
+            <a:off x="2844827" y="5165428"/>
+            <a:ext cx="1633509" cy="168376"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -12366,10 +11108,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="148" name="右矢印 147">
+          <xdr:cNvPr id="77" name="右矢印 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000094000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B676FDB-9EF0-4187-B489-DD80EB189CF7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12377,8 +11119,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="19186654">
-            <a:off x="2478790" y="5288454"/>
-            <a:ext cx="1778315" cy="195155"/>
+            <a:off x="3231911" y="5155952"/>
+            <a:ext cx="1580105" cy="186965"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -12519,190 +11261,1677 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>88446</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>70553</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>33945</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="155" name="図 154" descr="çå£ãªé¡ã®ãã¬ãã©ã³ã»ãªãã¬ã¼ã¿ã¼ã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="78" name="図 77" descr="çå£ãªé¡ã®ãã¬ãã©ã³ã»ãªãã¬ã¼ã¿ã¼ã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BD0CDD3-9342-4CBD-90D0-DB15570F6313}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="588950" y="3194335"/>
+            <a:ext cx="533900" cy="541475"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
           <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
             </a:ext>
           </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="80" name="図 79" descr="ãã½ã³ã³ãä½¿ãã¹ãã¼ãã¦ã§ã¢ãçãäººã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16FB49CB-C51D-4BAE-8803-25D247313989}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="608315" y="2143051"/>
+            <a:ext cx="533900" cy="548975"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
           <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
             </a:ext>
           </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="646339" y="3336254"/>
-          <a:ext cx="540000" cy="534905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="83" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99C1AEB1-9A50-43F8-A71F-DBA396504E78}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="548314" y="4442591"/>
+            <a:ext cx="542901" cy="1680357"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="eaVert" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>接続先システム</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>4</a:t>
+            </a:r>
+            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>136071</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>74839</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>118178</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>41035</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="165" name="図 164" descr="ãã½ã³ã³ãä½¿ãå¥³æ§ã®ã¤ã©ã¹ã">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="693964" y="2483303"/>
-          <a:ext cx="540000" cy="537696"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="84" name="グループ化 83">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45CEB5C7-FDAD-4F9B-9732-3CEC616D109B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1760431" y="4624110"/>
+            <a:ext cx="296049" cy="701879"/>
+            <a:chOff x="1762125" y="1781175"/>
+            <a:chExt cx="295275" cy="1190625"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="90" name="円/楕円 128">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E16BD55-C069-9F25-8DB0-F8298B5BACA7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1762125" y="1781175"/>
+              <a:ext cx="295275" cy="1190625"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="92" name="直線コネクタ 91">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90FBA3E-DED3-421E-B02D-CB616CD20CB8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="90" idx="1"/>
+              <a:endCxn id="90" idx="5"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1805367" y="1955538"/>
+              <a:ext cx="208791" cy="841899"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="93" name="直線コネクタ 92">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637E3562-31A2-C61F-3843-F27B0C826E71}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="90" idx="7"/>
+              <a:endCxn id="90" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="1805367" y="1955538"/>
+              <a:ext cx="208791" cy="841899"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="94" name="テキスト ボックス 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4FCE84-C8AA-4B4F-B682-3498613BE4DA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1598787" y="5113883"/>
+            <a:ext cx="636569" cy="144011"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>専用線</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="95" name="正方形/長方形 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{170D624C-5DD1-4D59-892E-B48F6C666299}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2687063" y="3784823"/>
+            <a:ext cx="728218" cy="330831"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent4"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>WEB3</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="98" name="右矢印 138">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179CBB36-6CEA-42AB-8910-FC12EAFEA35D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="19086508">
+            <a:off x="975868" y="4755949"/>
+            <a:ext cx="1850954" cy="215747"/>
+          </a:xfrm>
+          <a:prstGeom prst="rightArrow">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="6350">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>122464</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>74838</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>104571</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>43724</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="166" name="図 165" descr="ãã½ã³ã³ãä½¿ãã¹ãã¼ãã¦ã§ã¢ãçãäººã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A6000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="680357" y="1626052"/>
-          <a:ext cx="540000" cy="540386"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="99" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4265B873-D8FF-40C8-B03B-E3788EF79099}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="1031891" y="4172345"/>
+            <a:ext cx="1498634" cy="461614"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>API</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>連携</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(HTTPS/REST)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="100" name="正方形/長方形 99">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0444AD42-E448-4A07-8F97-5FA6CFD1FE96}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4295502" y="3791742"/>
+            <a:ext cx="1505955" cy="330831"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent4"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>REST</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" baseline="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t> API</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="157" name="正方形/長方形 156">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED59415-4701-4061-9CB0-DED7AB58A1EB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2696639" y="3786020"/>
+            <a:ext cx="3114395" cy="351417"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="20" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACF4A30-4281-8864-61FC-B49D5B39294A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:stCxn id="157" idx="3"/>
+            <a:endCxn id="79" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="5811034" y="3639208"/>
+            <a:ext cx="1117419" cy="322521"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="36" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D0F8DF1-A7C8-D21C-5848-EE8C7076B946}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:stCxn id="38" idx="3"/>
+            <a:endCxn id="45" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="5793026" y="3639208"/>
+            <a:ext cx="1562409" cy="832874"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="85" name="グループ化 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EB8EA20-3EBB-BE4C-FDF2-F1ABFB5B6BB3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="6672755" y="2773088"/>
+            <a:ext cx="910993" cy="879687"/>
+            <a:chOff x="6659617" y="2641708"/>
+            <a:chExt cx="910993" cy="879687"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="フローチャート : 磁気ディスク 100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B389504-078E-4CAD-9FC3-A8DB8780E41F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6659617" y="2641708"/>
+              <a:ext cx="910993" cy="879687"/>
+            </a:xfrm>
+            <a:prstGeom prst="flowChartMagneticDisk">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="CC99FF"/>
+            </a:solidFill>
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="9900CC"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent3"/>
+            </a:lnRef>
+            <a:fillRef idx="2">
+              <a:schemeClr val="accent3"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent3"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                </a:rPr>
+                <a:t>DB</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                </a:rPr>
+                <a:t>サーバ</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="正方形/長方形 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31833AC4-B49C-8984-3086-35A9D98D0854}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7182835" y="3229303"/>
+              <a:ext cx="318924" cy="278525"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="79" name="正方形/長方形 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B623185-3A5E-FF23-B1A7-18FE56355B05}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6755853" y="3229303"/>
+              <a:ext cx="318924" cy="278525"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="55" name="正方形/長方形 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF57B4A-2B4A-40D8-9F51-0883CCC83BC6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="20043632">
+            <a:off x="2988500" y="2506652"/>
+            <a:ext cx="4762344" cy="1767962"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>SAMPLE</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -13029,7 +13258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI423"/>
@@ -13045,131 +13274,131 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="1" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="1" t="s">
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="44"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="42"/>
+      <c r="AH1" s="42"/>
+      <c r="AI1" s="43"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="46"/>
       <c r="P2" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="57" t="s">
+      <c r="R2" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="62"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="58"/>
       <c r="Y3" s="11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="44"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="43"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13193,7 +13422,7 @@
     <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="14"/>
       <c r="D8" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13251,7 +13480,7 @@
     <row r="44" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="45" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D45" s="15" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13262,12 +13491,12 @@
         <v>2.2.</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D49" s="15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13302,13 +13531,13 @@
         <v>2.3.</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="14"/>
       <c r="D77" s="15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13318,7 +13547,7 @@
     </row>
     <row r="79" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D79" s="16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13333,7 +13562,7 @@
         <v>2.4.</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
@@ -13376,7 +13605,7 @@
         <v>2.4.1.</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18"/>
@@ -13452,7 +13681,7 @@
       <c r="C84" s="17"/>
       <c r="D84" s="19"/>
       <c r="E84" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="18"/>
@@ -13491,7 +13720,7 @@
       <c r="C85" s="17"/>
       <c r="D85" s="19"/>
       <c r="E85" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
@@ -13567,19 +13796,19 @@
       <c r="C87" s="17"/>
       <c r="D87" s="19"/>
       <c r="E87" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F87" s="21"/>
       <c r="G87" s="22"/>
       <c r="H87" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I87" s="21"/>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
       <c r="L87" s="22"/>
       <c r="M87" s="20" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="N87" s="21"/>
       <c r="O87" s="21"/>
@@ -13609,20 +13838,20 @@
       <c r="B88" s="18"/>
       <c r="C88" s="17"/>
       <c r="D88" s="19"/>
-      <c r="E88" s="32" t="s">
-        <v>23</v>
+      <c r="E88" s="31" t="s">
+        <v>28</v>
       </c>
-      <c r="F88" s="33"/>
-      <c r="G88" s="34"/>
-      <c r="H88" s="38" t="s">
-        <v>31</v>
+      <c r="F88" s="32"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="37" t="s">
+        <v>29</v>
       </c>
-      <c r="I88" s="33"/>
-      <c r="J88" s="33"/>
-      <c r="K88" s="33"/>
-      <c r="L88" s="34"/>
+      <c r="I88" s="32"/>
+      <c r="J88" s="32"/>
+      <c r="K88" s="32"/>
+      <c r="L88" s="33"/>
       <c r="M88" s="23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N88" s="24"/>
       <c r="O88" s="24"/>
@@ -13652,38 +13881,38 @@
       <c r="B89" s="18"/>
       <c r="C89" s="17"/>
       <c r="D89" s="19"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="40"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="40"/>
-      <c r="J89" s="40"/>
-      <c r="K89" s="40"/>
-      <c r="L89" s="41"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="40"/>
       <c r="M89" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
-      <c r="N89" s="27"/>
-      <c r="O89" s="27"/>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="27"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-      <c r="U89" s="27"/>
-      <c r="V89" s="27"/>
-      <c r="W89" s="27"/>
-      <c r="X89" s="27"/>
-      <c r="Y89" s="27"/>
-      <c r="Z89" s="27"/>
-      <c r="AA89" s="27"/>
-      <c r="AB89" s="27"/>
-      <c r="AC89" s="27"/>
-      <c r="AD89" s="27"/>
-      <c r="AE89" s="27"/>
-      <c r="AF89" s="27"/>
-      <c r="AG89" s="27"/>
-      <c r="AH89" s="28"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+      <c r="P89" s="18"/>
+      <c r="Q89" s="18"/>
+      <c r="R89" s="18"/>
+      <c r="S89" s="18"/>
+      <c r="T89" s="18"/>
+      <c r="U89" s="18"/>
+      <c r="V89" s="18"/>
+      <c r="W89" s="18"/>
+      <c r="X89" s="18"/>
+      <c r="Y89" s="18"/>
+      <c r="Z89" s="18"/>
+      <c r="AA89" s="18"/>
+      <c r="AB89" s="18"/>
+      <c r="AC89" s="18"/>
+      <c r="AD89" s="18"/>
+      <c r="AE89" s="18"/>
+      <c r="AF89" s="18"/>
+      <c r="AG89" s="18"/>
+      <c r="AH89" s="27"/>
       <c r="AI89" s="18"/>
     </row>
     <row r="90" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13691,20 +13920,20 @@
       <c r="B90" s="18"/>
       <c r="C90" s="17"/>
       <c r="D90" s="19"/>
-      <c r="E90" s="32" t="s">
-        <v>25</v>
+      <c r="E90" s="31" t="s">
+        <v>32</v>
       </c>
-      <c r="F90" s="33"/>
-      <c r="G90" s="34"/>
-      <c r="H90" s="32" t="s">
+      <c r="F90" s="32"/>
+      <c r="G90" s="33"/>
+      <c r="H90" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I90" s="32"/>
+      <c r="J90" s="32"/>
+      <c r="K90" s="32"/>
+      <c r="L90" s="33"/>
+      <c r="M90" s="23" t="s">
         <v>34</v>
-      </c>
-      <c r="I90" s="33"/>
-      <c r="J90" s="33"/>
-      <c r="K90" s="33"/>
-      <c r="L90" s="34"/>
-      <c r="M90" s="23" t="s">
-        <v>33</v>
       </c>
       <c r="N90" s="24"/>
       <c r="O90" s="24"/>
@@ -13734,36 +13963,36 @@
       <c r="B91" s="18"/>
       <c r="C91" s="17"/>
       <c r="D91" s="19"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="36"/>
-      <c r="J91" s="36"/>
-      <c r="K91" s="36"/>
-      <c r="L91" s="37"/>
-      <c r="M91" s="29"/>
-      <c r="N91" s="30"/>
-      <c r="O91" s="30"/>
-      <c r="P91" s="30"/>
-      <c r="Q91" s="30"/>
-      <c r="R91" s="30"/>
-      <c r="S91" s="30"/>
-      <c r="T91" s="30"/>
-      <c r="U91" s="30"/>
-      <c r="V91" s="30"/>
-      <c r="W91" s="30"/>
-      <c r="X91" s="30"/>
-      <c r="Y91" s="30"/>
-      <c r="Z91" s="30"/>
-      <c r="AA91" s="30"/>
-      <c r="AB91" s="30"/>
-      <c r="AC91" s="30"/>
-      <c r="AD91" s="30"/>
-      <c r="AE91" s="30"/>
-      <c r="AF91" s="30"/>
-      <c r="AG91" s="30"/>
-      <c r="AH91" s="31"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="34"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="35"/>
+      <c r="L91" s="36"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="29"/>
+      <c r="O91" s="29"/>
+      <c r="P91" s="29"/>
+      <c r="Q91" s="29"/>
+      <c r="R91" s="29"/>
+      <c r="S91" s="29"/>
+      <c r="T91" s="29"/>
+      <c r="U91" s="29"/>
+      <c r="V91" s="29"/>
+      <c r="W91" s="29"/>
+      <c r="X91" s="29"/>
+      <c r="Y91" s="29"/>
+      <c r="Z91" s="29"/>
+      <c r="AA91" s="29"/>
+      <c r="AB91" s="29"/>
+      <c r="AC91" s="29"/>
+      <c r="AD91" s="29"/>
+      <c r="AE91" s="29"/>
+      <c r="AF91" s="29"/>
+      <c r="AG91" s="29"/>
+      <c r="AH91" s="30"/>
       <c r="AI91" s="18"/>
     </row>
     <row r="92" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -14154,7 +14383,7 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="D79" r:id="rId1" display="https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/nablarch/big_picture.html" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D79" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId2"/>

--- a/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CB5B99-5C5B-4D03-B141-BF7A482A7A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884DDAE2-A929-4B09-9A6F-4645D82B78C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5942,10 +5942,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="87" name="グループ化 86">
+        <xdr:cNvPr id="14" name="グループ化 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95EA71B2-7203-B593-A30D-B714737D7062}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE4FFCD2-9423-3A59-064D-CD3EAC3FFDFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5955,8 +5955,8 @@
         <a:xfrm>
           <a:off x="296008" y="1339077"/>
           <a:ext cx="9101992" cy="4836966"/>
-          <a:chOff x="295680" y="1356156"/>
-          <a:chExt cx="9091153" cy="4892803"/>
+          <a:chOff x="296008" y="1339077"/>
+          <a:chExt cx="9101992" cy="4836966"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -5974,8 +5974,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2423622" y="1513020"/>
-            <a:ext cx="5672135" cy="3444475"/>
+            <a:off x="2426487" y="1494151"/>
+            <a:ext cx="5678898" cy="3405166"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6126,8 +6126,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4106865" y="1854180"/>
-            <a:ext cx="1846084" cy="2947228"/>
+            <a:off x="4111737" y="1831418"/>
+            <a:ext cx="1848285" cy="2913594"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6295,8 +6295,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="5778685" y="4914667"/>
-            <a:ext cx="278933" cy="879203"/>
+            <a:off x="5787308" y="4851437"/>
+            <a:ext cx="275750" cy="880251"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -6445,8 +6445,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1759154" y="2980436"/>
-            <a:ext cx="296049" cy="701879"/>
+            <a:off x="1761227" y="2944821"/>
+            <a:ext cx="296402" cy="693869"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -6595,8 +6595,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1759154" y="2055581"/>
-            <a:ext cx="296049" cy="759221"/>
+            <a:off x="1761227" y="2030520"/>
+            <a:ext cx="296402" cy="750557"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -6747,8 +6747,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="8843932" y="1503934"/>
-            <a:ext cx="542901" cy="3761436"/>
+            <a:off x="8854452" y="1485169"/>
+            <a:ext cx="543548" cy="3718510"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6894,8 +6894,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2601950" y="1863266"/>
-            <a:ext cx="898444" cy="2773110"/>
+            <a:off x="2605028" y="1840400"/>
+            <a:ext cx="899515" cy="2741463"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7065,8 +7065,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="295680" y="2621904"/>
-            <a:ext cx="1246225" cy="234739"/>
+            <a:off x="296008" y="2590380"/>
+            <a:ext cx="1247711" cy="232060"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7220,8 +7220,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5997996" y="5428632"/>
-            <a:ext cx="1518057" cy="408659"/>
+            <a:off x="6005123" y="5365078"/>
+            <a:ext cx="1519867" cy="403995"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7383,8 +7383,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="6026628" y="1821757"/>
-            <a:ext cx="1869733" cy="254706"/>
+            <a:off x="6033789" y="1799365"/>
+            <a:ext cx="1871962" cy="251799"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7552,8 +7552,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2687063" y="2187585"/>
-            <a:ext cx="728218" cy="325240"/>
+            <a:off x="2690242" y="2161018"/>
+            <a:ext cx="729086" cy="321528"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7701,8 +7701,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2687063" y="2740164"/>
-            <a:ext cx="728218" cy="324639"/>
+            <a:off x="2690242" y="2707291"/>
+            <a:ext cx="729086" cy="320934"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7850,8 +7850,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4298995" y="2193199"/>
-            <a:ext cx="1502463" cy="325240"/>
+            <a:off x="4304096" y="2166568"/>
+            <a:ext cx="1504254" cy="321528"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8007,8 +8007,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4295502" y="2728033"/>
-            <a:ext cx="1505955" cy="324639"/>
+            <a:off x="4300599" y="2695298"/>
+            <a:ext cx="1507750" cy="320934"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8164,8 +8164,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4281323" y="4321895"/>
-            <a:ext cx="1511703" cy="300373"/>
+            <a:off x="4286403" y="4270971"/>
+            <a:ext cx="1513505" cy="296945"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8308,8 +8308,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2696639" y="2722311"/>
-            <a:ext cx="3114395" cy="361591"/>
+            <a:off x="2699830" y="2689641"/>
+            <a:ext cx="3118108" cy="357464"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8453,8 +8453,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2685860" y="2185401"/>
-            <a:ext cx="3140249" cy="366448"/>
+            <a:off x="2689038" y="2158859"/>
+            <a:ext cx="3143993" cy="362266"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8602,8 +8602,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5801457" y="2890353"/>
-            <a:ext cx="871298" cy="322579"/>
+            <a:off x="5808349" y="2855766"/>
+            <a:ext cx="872337" cy="318898"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -8647,8 +8647,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5103583" y="5857151"/>
-            <a:ext cx="3849000" cy="391808"/>
+            <a:off x="5109643" y="5788706"/>
+            <a:ext cx="1938857" cy="387337"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8794,8 +8794,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4119438" y="5443149"/>
-            <a:ext cx="1870630" cy="388216"/>
+            <a:off x="4124325" y="5379429"/>
+            <a:ext cx="1872860" cy="383786"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8986,8 +8986,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5801458" y="2355819"/>
-            <a:ext cx="1326794" cy="417269"/>
+            <a:off x="5808350" y="2327332"/>
+            <a:ext cx="1328376" cy="412507"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -9027,8 +9027,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="3950322">
-            <a:off x="5094495" y="5222401"/>
-            <a:ext cx="1119530" cy="154722"/>
+            <a:off x="5107600" y="5160225"/>
+            <a:ext cx="1106754" cy="154906"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -9184,8 +9184,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1420940" y="5857150"/>
-            <a:ext cx="2507796" cy="391808"/>
+            <a:off x="1422610" y="5788705"/>
+            <a:ext cx="2510786" cy="387337"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9331,8 +9331,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1697074" y="5325293"/>
-            <a:ext cx="1290633" cy="355399"/>
+            <a:off x="1699073" y="5262918"/>
+            <a:ext cx="1292172" cy="351343"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9494,8 +9494,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="3233853" y="5712848"/>
-            <a:ext cx="1419843" cy="337383"/>
+            <a:off x="3237684" y="5646050"/>
+            <a:ext cx="1421536" cy="333533"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9655,8 +9655,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="14796441">
-            <a:off x="5278793" y="5160908"/>
-            <a:ext cx="1148895" cy="187527"/>
+            <a:off x="5292303" y="5099227"/>
+            <a:ext cx="1135784" cy="187751"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -9812,8 +9812,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1245726" y="1356156"/>
-            <a:ext cx="1225748" cy="453973"/>
+            <a:off x="1247187" y="1339077"/>
+            <a:ext cx="1227209" cy="448792"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9984,8 +9984,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1142215" y="2368625"/>
-            <a:ext cx="1543645" cy="49924"/>
+            <a:off x="1143552" y="2339992"/>
+            <a:ext cx="1545485" cy="49354"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -10027,8 +10027,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1238982" y="2901275"/>
-            <a:ext cx="1457657" cy="500687"/>
+            <a:off x="1240435" y="2866563"/>
+            <a:ext cx="1459395" cy="494973"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -10068,8 +10068,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1545817" y="2529418"/>
-            <a:ext cx="774418" cy="171271"/>
+            <a:off x="1547635" y="2498950"/>
+            <a:ext cx="775341" cy="169316"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10126,8 +10126,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1597509" y="3439730"/>
-            <a:ext cx="619338" cy="144011"/>
+            <a:off x="1599389" y="3398873"/>
+            <a:ext cx="620076" cy="142368"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10186,8 +10186,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="362027" y="3751806"/>
-            <a:ext cx="1345838" cy="228045"/>
+            <a:off x="362434" y="3707388"/>
+            <a:ext cx="1347443" cy="225443"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10339,8 +10339,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="8326704" y="1960197"/>
-            <a:ext cx="296048" cy="701879"/>
+            <a:off x="8336607" y="1936225"/>
+            <a:ext cx="296401" cy="693869"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -10489,8 +10489,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8165059" y="2419490"/>
-            <a:ext cx="636898" cy="144011"/>
+            <a:off x="8174769" y="2390276"/>
+            <a:ext cx="637657" cy="142368"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10547,8 +10547,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5888822" y="2034540"/>
-            <a:ext cx="2909688" cy="221131"/>
+            <a:off x="5895818" y="2009719"/>
+            <a:ext cx="2913157" cy="218607"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10698,8 +10698,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6154753" y="5176417"/>
-            <a:ext cx="643791" cy="142369"/>
+            <a:off x="6162067" y="5115741"/>
+            <a:ext cx="644559" cy="140744"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10756,8 +10756,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="3316716" y="4628405"/>
-            <a:ext cx="278933" cy="1397206"/>
+            <a:off x="3322404" y="4565177"/>
+            <a:ext cx="275750" cy="1398872"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -10906,8 +10906,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2464978" y="5075337"/>
-            <a:ext cx="619339" cy="144010"/>
+            <a:off x="2467892" y="5015814"/>
+            <a:ext cx="620077" cy="142367"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10964,8 +10964,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="8439195">
-            <a:off x="2844827" y="5165428"/>
-            <a:ext cx="1633509" cy="168376"/>
+            <a:off x="2848194" y="5104877"/>
+            <a:ext cx="1635457" cy="166454"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -11119,8 +11119,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="19186654">
-            <a:off x="3231911" y="5155952"/>
-            <a:ext cx="1580105" cy="186965"/>
+            <a:off x="3235740" y="5095509"/>
+            <a:ext cx="1581989" cy="184831"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -11289,8 +11289,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="588950" y="3194335"/>
-            <a:ext cx="533900" cy="541475"/>
+            <a:off x="589628" y="3156279"/>
+            <a:ext cx="534537" cy="535296"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11335,8 +11335,8 @@
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="608315" y="2143051"/>
-            <a:ext cx="533900" cy="548975"/>
+            <a:off x="609016" y="2116992"/>
+            <a:ext cx="534537" cy="542710"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11368,8 +11368,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="548314" y="4442591"/>
-            <a:ext cx="542901" cy="1680357"/>
+            <a:off x="548943" y="4390289"/>
+            <a:ext cx="543548" cy="1661181"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11532,8 +11532,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1760431" y="4624110"/>
-            <a:ext cx="296049" cy="701879"/>
+            <a:off x="1762505" y="4569737"/>
+            <a:ext cx="296402" cy="693869"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
@@ -11682,8 +11682,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1598787" y="5113883"/>
-            <a:ext cx="636569" cy="144011"/>
+            <a:off x="1600669" y="5053921"/>
+            <a:ext cx="637328" cy="142368"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11740,8 +11740,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2687063" y="3784823"/>
-            <a:ext cx="728218" cy="330831"/>
+            <a:off x="2690242" y="3740028"/>
+            <a:ext cx="729086" cy="327056"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11889,8 +11889,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="19086508">
-            <a:off x="975868" y="4755949"/>
-            <a:ext cx="1850954" cy="215747"/>
+            <a:off x="977007" y="4700071"/>
+            <a:ext cx="1853161" cy="213285"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -12042,8 +12042,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1031891" y="4172345"/>
-            <a:ext cx="1498634" cy="461614"/>
+            <a:off x="1033097" y="4123127"/>
+            <a:ext cx="1500421" cy="456346"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12219,8 +12219,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4295502" y="3791742"/>
-            <a:ext cx="1505955" cy="330831"/>
+            <a:off x="4300599" y="3746868"/>
+            <a:ext cx="1507750" cy="327056"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12376,8 +12376,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2696639" y="3786020"/>
-            <a:ext cx="3114395" cy="351417"/>
+            <a:off x="2699830" y="3741211"/>
+            <a:ext cx="3118108" cy="347407"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12519,8 +12519,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="5811034" y="3639208"/>
-            <a:ext cx="1117419" cy="322521"/>
+            <a:off x="5817938" y="3596075"/>
+            <a:ext cx="1118751" cy="318840"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -12555,14 +12555,13 @@
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:cxnSpLocks/>
-            <a:stCxn id="38" idx="3"/>
             <a:endCxn id="45" idx="2"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="5793026" y="3639208"/>
-            <a:ext cx="1562409" cy="832874"/>
+            <a:off x="5802289" y="3596074"/>
+            <a:ext cx="1561300" cy="757886"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -12599,8 +12598,8 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="6672755" y="2773088"/>
-            <a:ext cx="910993" cy="879687"/>
+            <a:off x="6680686" y="2739839"/>
+            <a:ext cx="912079" cy="869648"/>
             <a:chOff x="6659617" y="2641708"/>
             <a:chExt cx="910993" cy="879687"/>
           </a:xfrm>
@@ -12885,8 +12884,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="20043632">
-            <a:off x="2988500" y="2506652"/>
-            <a:ext cx="4762344" cy="1767962"/>
+            <a:off x="2992039" y="2476443"/>
+            <a:ext cx="4768022" cy="1747786"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12928,6 +12927,368 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C920392B-4601-B6A5-1373-D3B461274E36}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6991350" y="4581524"/>
+            <a:ext cx="1076325" cy="276225"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>SMTP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>サーバー</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="3" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6FA7AE5-5EE5-DD09-446C-B5E61C2E4CC8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:endCxn id="2" idx="1"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5814851" y="4477250"/>
+            <a:ext cx="1176499" cy="242387"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="29" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F40A95B-9DA8-4CAB-8DBB-04B87B0F1E08}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="5677959" y="4689976"/>
+            <a:ext cx="1216017" cy="262432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>メール送信</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(SMTP)</a:t>
+            </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>

--- a/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_2全体概要.xlsx
@@ -1,24 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1F824C-2EBB-4943-82D8-8D19382EC710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884DDAE2-A929-4B09-9A6F-4645D82B78C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.全体概要" sheetId="13" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2.全体概要'!$A$1:$AI$93</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'2.全体概要'!$A$1:$AI$79</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,11 +37,25 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>XXXプロジェクト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>工程</t>
     <rPh sb="0" eb="2">
       <t>コウテイ</t>
     </rPh>
     <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>要件定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>作成</t>
@@ -57,6 +69,9 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>アプリケーション方式設計書</t>
+  </si>
+  <si>
     <t>変更</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -66,19 +81,6 @@
   <si>
     <t>確認</t>
     <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>アプリケーション方式設計書</t>
-  </si>
-  <si>
-    <t>理由</t>
-    <rPh sb="0" eb="2">
-      <t>リユウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アプリケーション・アーキテクチャ</t>
   </si>
   <si>
     <t>2.</t>
@@ -105,6 +107,25 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>本システムで稼働するアプリケーションの全体図を以下に記載する。</t>
+  </si>
+  <si>
+    <t>※WEBサーバー・Applicationサーバーは複数台で構成し、前段にロードバランサーを配置する。</t>
+    <rPh sb="25" eb="28">
+      <t>フクスウダイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゼンダン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>ソフトウェア構成</t>
     <rPh sb="6" eb="8">
       <t>コウセイ</t>
@@ -115,24 +136,10 @@
     <t>本アプリケーションのソフトウェア構成は以下の通り。</t>
   </si>
   <si>
-    <t>本システムのアプリケーション・アーキテクチャは、Nablarch Application Frameworkをベースとする。</t>
+    <t>アプリケーション・アーキテクチャ</t>
   </si>
   <si>
-    <t>本システムで稼働するアプリケーションの全体図を以下に記載する。</t>
-  </si>
-  <si>
-    <t>XXXプロジェクト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>要件定義</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <t>本システムのアプリケーション・アーキテクチャは、Nablarch Application Frameworkをベースとする。</t>
   </si>
   <si>
     <t>Nablarch が提供するアプリケーション・アーキテクチャについては、以下のNablarch解説書を参照。</t>
@@ -148,6 +155,10 @@
     <rPh sb="51" eb="53">
       <t>サンショウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/nablarch/big_picture.html</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -168,18 +179,6 @@
     <rPh sb="28" eb="29">
       <t>トオ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Java</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ソフトウェア</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Nablarch</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -220,10 +219,29 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>ソフトウェア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>種類およびバージョン</t>
     <rPh sb="0" eb="2">
       <t>シュルイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>理由</t>
+    <rPh sb="0" eb="2">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Java</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RedHat OpenJDK 21</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -240,30 +258,6 @@
     <rPh sb="38" eb="40">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>※WEBサーバー・Applicationサーバーは複数台で構成し、前段にロードバランサーを配置する。</t>
-    <rPh sb="25" eb="28">
-      <t>フクスウダイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ゼンダン</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ハイチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/nablarch/big_picture.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>RedHat OpenJDK 21</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -292,6 +286,14 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>Nablarch</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>6u2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>2024年9月現在最新バージョンである6u2を選択する。</t>
     <rPh sb="4" eb="5">
       <t>ネン</t>
@@ -308,10 +310,6 @@
     <rPh sb="23" eb="25">
       <t>センタク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>6u2</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -554,47 +552,47 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -636,9 +634,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -675,19 +670,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -708,23 +703,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -744,7 +730,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -785,17 +771,17 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>250975</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="192" name="グループ化 191">
+        <xdr:cNvPr id="171" name="グループ化 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C0000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E17E99-7FE1-9C30-829C-4EEDC7FBD431}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -804,9 +790,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="828675" y="7229475"/>
-          <a:ext cx="8610600" cy="3476626"/>
-          <a:chOff x="63212" y="3335473"/>
-          <a:chExt cx="8773832" cy="3306750"/>
+          <a:ext cx="7985275" cy="3476626"/>
+          <a:chOff x="828675" y="7229475"/>
+          <a:chExt cx="7985275" cy="3476626"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -822,8 +808,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2540583" y="6280273"/>
-            <a:ext cx="6277203" cy="361950"/>
+            <a:off x="2650356" y="10325557"/>
+            <a:ext cx="6163594" cy="380544"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -966,8 +952,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4187504" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="4266637" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1113,8 +1099,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5348895" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="5406421" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1262,8 +1248,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6501023" y="6367469"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="6537114" y="10417232"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1432,8 +1418,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2972631" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="3074366" y="10417231"/>
+            <a:ext cx="1063082" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1582,8 +1568,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124077" y="5733256"/>
-            <a:ext cx="8624387" cy="251511"/>
+            <a:off x="888408" y="9750438"/>
+            <a:ext cx="7826967" cy="264432"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1736,8 +1722,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7709050" y="6367468"/>
-            <a:ext cx="1080000" cy="173700"/>
+            <a:off x="7725842" y="10417231"/>
+            <a:ext cx="1059907" cy="182623"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1894,8 +1880,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124076" y="5496803"/>
-            <a:ext cx="2343119" cy="218680"/>
+            <a:off x="888408" y="9501838"/>
+            <a:ext cx="1505543" cy="229914"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2091,8 +2077,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="124077" y="4598329"/>
-            <a:ext cx="728643" cy="898475"/>
+            <a:off x="888408" y="8557207"/>
+            <a:ext cx="470492" cy="944632"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2240,8 +2226,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="859586" y="4598072"/>
-            <a:ext cx="822119" cy="901012"/>
+            <a:off x="1359409" y="8556937"/>
+            <a:ext cx="529632" cy="947299"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2404,8 +2390,667 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1683419" y="4598329"/>
-            <a:ext cx="776817" cy="898473"/>
+            <a:off x="1891689" y="8557207"/>
+            <a:ext cx="500442" cy="944630"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Apache</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="205" name="正方形/長方形 204">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CD000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2574925" y="9501837"/>
+            <a:ext cx="4269018" cy="248600"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>仮想</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>OS</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>（</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>RHEL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>）</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="206" name="正方形/長方形 205">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2581997" y="8557207"/>
+            <a:ext cx="475528" cy="944632"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>vSphere Data Protection</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="207" name="正方形/長方形 206">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CF000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3059074" y="8556938"/>
+            <a:ext cx="446126" cy="947298"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>ServerProtect</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>for Linux</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="208" name="正方形/長方形 207">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D0000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4140200" y="8829676"/>
+            <a:ext cx="1788806" cy="208800"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2535,17 +3180,17 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>Apache</a:t>
+              <a:t>Tomcat</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="205" name="正方形/長方形 204">
+          <xdr:cNvPr id="209" name="正方形/長方形 208">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CD000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D1000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2553,8 +3198,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2771799" y="5496802"/>
-            <a:ext cx="3420713" cy="236453"/>
+            <a:off x="4140200" y="9047391"/>
+            <a:ext cx="2703744" cy="456844"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2563,13 +3208,13 @@
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:lnRef>
           <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:fillRef>
           <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent5"/>
           </a:effectRef>
           <a:fontRef idx="minor">
             <a:schemeClr val="dk1"/>
@@ -2675,7 +3320,7 @@
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
                 <a:solidFill>
                   <a:schemeClr val="tx2">
                     <a:lumMod val="75000"/>
@@ -2684,65 +3329,17 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>仮想</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>OS</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>（</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>RHEL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>）</a:t>
+              <a:t>JDK(OpenJDK 21)</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="206" name="正方形/長方形 205">
+          <xdr:cNvPr id="210" name="正方形/長方形 209">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2750,8 +3347,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2771801" y="4598329"/>
-            <a:ext cx="484543" cy="898475"/>
+            <a:off x="3501453" y="8557857"/>
+            <a:ext cx="279972" cy="938193"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2881,617 +3478,6 @@
                 <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>vSphere Data Protection</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="207" name="正方形/長方形 206">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CF000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3257922" y="4598073"/>
-            <a:ext cx="454583" cy="901011"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ServerProtect</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>for Linux</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="208" name="正方形/長方形 207">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D0000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4350091" y="4857484"/>
-            <a:ext cx="910140" cy="198598"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>Tomcat</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="209" name="正方形/長方形 208">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D1000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4347149" y="5064561"/>
-            <a:ext cx="1845364" cy="434522"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>JDK(OpenJDK 21)</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="210" name="正方形/長方形 209">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3708687" y="4598947"/>
-            <a:ext cx="285279" cy="892351"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent5"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent5"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
-                <a:solidFill>
-                  <a:schemeClr val="tx2">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
               <a:t>HULFT</a:t>
             </a:r>
           </a:p>
@@ -3510,8 +3496,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4350093" y="4598638"/>
-            <a:ext cx="910138" cy="252375"/>
+            <a:off x="5035801" y="8557532"/>
+            <a:ext cx="893205" cy="265340"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3664,8 +3650,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4338271" y="3919169"/>
-            <a:ext cx="908230" cy="663735"/>
+            <a:off x="5024199" y="7843157"/>
+            <a:ext cx="891333" cy="697833"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3854,8 +3840,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6477353" y="5516989"/>
-            <a:ext cx="2271111" cy="218680"/>
+            <a:off x="7123485" y="9523061"/>
+            <a:ext cx="1591890" cy="229914"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4051,8 +4037,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6477354" y="4586591"/>
-            <a:ext cx="739483" cy="930401"/>
+            <a:off x="7134224" y="8544866"/>
+            <a:ext cx="514961" cy="978198"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4200,8 +4186,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7223703" y="4586866"/>
-            <a:ext cx="699976" cy="932403"/>
+            <a:off x="7660807" y="8545155"/>
+            <a:ext cx="485220" cy="980303"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4364,8 +4350,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7930826" y="4586563"/>
-            <a:ext cx="818412" cy="930669"/>
+            <a:off x="8148220" y="8544837"/>
+            <a:ext cx="569883" cy="978480"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4387,7 +4373,7 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vert="vert" wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
           <a:lstStyle>
             <a:defPPr>
               <a:defRPr lang="ja-JP"/>
@@ -4513,8 +4499,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2699792" y="3345343"/>
-            <a:ext cx="3600400" cy="2747952"/>
+            <a:off x="2530475" y="7239852"/>
+            <a:ext cx="4419145" cy="2889121"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4687,8 +4673,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4003672" y="4598947"/>
-            <a:ext cx="336611" cy="892351"/>
+            <a:off x="3794125" y="8557857"/>
+            <a:ext cx="330349" cy="938193"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4836,8 +4822,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6372199" y="3335473"/>
-            <a:ext cx="2464845" cy="2757823"/>
+            <a:off x="7020288" y="7229475"/>
+            <a:ext cx="1783988" cy="2899499"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5010,8 +4996,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="63212" y="3345343"/>
-            <a:ext cx="2464845" cy="2747952"/>
+            <a:off x="828675" y="7239852"/>
+            <a:ext cx="1622425" cy="2889121"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5184,8 +5170,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5253366" y="4592167"/>
-            <a:ext cx="940545" cy="465921"/>
+            <a:off x="5922269" y="8550729"/>
+            <a:ext cx="923047" cy="489857"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5338,8 +5324,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5246501" y="3919169"/>
-            <a:ext cx="954274" cy="663735"/>
+            <a:off x="5915532" y="7843157"/>
+            <a:ext cx="936520" cy="697833"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5535,102 +5521,431 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="169" name="正方形/長方形 168">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B651FC0-E278-80C7-E48C-D1EA58E201E7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4140451" y="8557532"/>
+            <a:ext cx="890030" cy="265340"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent2"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent2"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent2"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Nablarch</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="170" name="正方形/長方形 169">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F254B2E8-EFAF-E6D0-6C4E-613EA3F888AD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4141549" y="7843157"/>
+            <a:ext cx="888158" cy="697833"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" lIns="36000" rIns="36000" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>業務</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>アプリケーション</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(REST API)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="162" name="正方形/長方形 161">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="20043632">
+            <a:off x="2784489" y="8055504"/>
+            <a:ext cx="4773206" cy="2445229"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>SAMPLE</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>98441</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>92606</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>175822</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>108960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="162" name="正方形/長方形 161">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="20043632">
-          <a:off x="3413141" y="7636406"/>
-          <a:ext cx="4773206" cy="2445229"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>SAMPLE</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:colOff>19783</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>81777</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>60993</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="グループ化 1">
+        <xdr:cNvPr id="14" name="グループ化 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE4FFCD2-9423-3A59-064D-CD3EAC3FFDFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5638,18 +5953,341 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="361950" y="1339077"/>
-          <a:ext cx="9036050" cy="4944248"/>
-          <a:chOff x="339725" y="1313677"/>
-          <a:chExt cx="8324850" cy="5182373"/>
+          <a:off x="296008" y="1339077"/>
+          <a:ext cx="9101992" cy="4836966"/>
+          <a:chOff x="296008" y="1339077"/>
+          <a:chExt cx="9101992" cy="4836966"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA608710-AA6F-4D02-B913-2DF03E93065E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="2426487" y="1494151"/>
+            <a:ext cx="5678898" cy="3405166"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFCC"/>
+          </a:solidFill>
+          <a:ln w="31750">
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>XXX</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>システム</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4ACDA9-6EE9-48F6-A3F1-0F4D6190EA75}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="4111737" y="1831418"/>
+            <a:ext cx="1848285" cy="2913594"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>Application</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>サーバ</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="137" name="グループ化 136">
+          <xdr:cNvPr id="5" name="グループ化 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000089000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3022DEAD-879D-4481-93D4-B0B50524E849}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5657,18 +6295,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="5320506" y="4963317"/>
-            <a:ext cx="288925" cy="811213"/>
+            <a:off x="5787308" y="4851437"/>
+            <a:ext cx="275750" cy="880251"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="140" name="円/楕円 139">
+            <xdr:cNvPr id="6" name="円/楕円 139">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A94CAE69-A36E-9EEF-80F8-2A9EAC69722E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5717,16 +6355,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="141" name="直線コネクタ 140">
+            <xdr:cNvPr id="7" name="直線コネクタ 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DCAB10-44A4-E652-87ED-1928760CA3A5}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="140" idx="1"/>
-              <a:endCxn id="140" idx="5"/>
+              <a:stCxn id="6" idx="1"/>
+              <a:endCxn id="6" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5756,16 +6394,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="142" name="直線コネクタ 141">
+            <xdr:cNvPr id="8" name="直線コネクタ 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B68F3499-16E9-E2E0-4155-5E6D03953CEB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="140" idx="7"/>
-              <a:endCxn id="140" idx="3"/>
+              <a:stCxn id="6" idx="7"/>
+              <a:endCxn id="6" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5796,10 +6434,10 @@
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="110" name="グループ化 109">
+          <xdr:cNvPr id="9" name="グループ化 8">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D291FC0-3000-4F6B-A209-671F8956A55F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5807,18 +6445,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1628775" y="3235324"/>
-            <a:ext cx="273050" cy="727076"/>
+            <a:off x="1761227" y="2944821"/>
+            <a:ext cx="296402" cy="693869"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="111" name="円/楕円 110">
+            <xdr:cNvPr id="10" name="円/楕円 110">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{978C39C3-A67C-2356-E087-03ECC87F0280}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5867,16 +6505,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="115" name="直線コネクタ 114">
+            <xdr:cNvPr id="11" name="直線コネクタ 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D6A886-097E-27C5-EC6D-A1B307233B4D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="111" idx="1"/>
-              <a:endCxn id="111" idx="5"/>
+              <a:stCxn id="10" idx="1"/>
+              <a:endCxn id="10" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5906,16 +6544,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="116" name="直線コネクタ 115">
+            <xdr:cNvPr id="13" name="直線コネクタ 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572E2F6F-0D57-E01F-535C-D113D5E00AA0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="111" idx="7"/>
-              <a:endCxn id="111" idx="3"/>
+              <a:stCxn id="10" idx="7"/>
+              <a:endCxn id="10" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -5946,10 +6584,10 @@
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="19" name="グループ化 18">
+          <xdr:cNvPr id="15" name="グループ化 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28DB3A29-8298-4285-B1D3-2D47F78D4427}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5957,18 +6595,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1628775" y="1924050"/>
-            <a:ext cx="273050" cy="977900"/>
+            <a:off x="1761227" y="2030520"/>
+            <a:ext cx="296402" cy="750557"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="円/楕円 11">
+            <xdr:cNvPr id="16" name="円/楕円 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FECAEB3C-5884-E3D7-A3C9-9C775B3429F0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6017,16 +6655,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="14" name="直線コネクタ 13">
+            <xdr:cNvPr id="17" name="直線コネクタ 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5988C8B3-1D45-B160-F099-1E2759E30D44}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="12" idx="1"/>
-              <a:endCxn id="12" idx="5"/>
+              <a:stCxn id="16" idx="1"/>
+              <a:endCxn id="16" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -6056,16 +6694,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="109" name="直線コネクタ 108">
+            <xdr:cNvPr id="18" name="直線コネクタ 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C02A634A-BBC2-5CE9-37DF-3C951DA9D8D7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="12" idx="7"/>
-              <a:endCxn id="12" idx="3"/>
+              <a:stCxn id="16" idx="7"/>
+              <a:endCxn id="16" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -6096,10 +6734,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="85" name="Rectangle 37">
+          <xdr:cNvPr id="22" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03036546-3D11-4F19-904C-44CB893CE0C8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6109,160 +6747,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2241550" y="1476375"/>
-            <a:ext cx="5232053" cy="3387725"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFFCC"/>
-          </a:solidFill>
-          <a:ln w="31750">
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>XXX</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>システム</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="86" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="8163799" y="1466850"/>
-            <a:ext cx="500776" cy="3897840"/>
+            <a:off x="8854452" y="1485169"/>
+            <a:ext cx="543548" cy="3718510"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6395,10 +6881,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="87" name="Rectangle 37">
+          <xdr:cNvPr id="23" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCC3881-A349-48BB-8650-E411667E6D2F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6408,8 +6894,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2406145" y="1838326"/>
-            <a:ext cx="828638" cy="1863724"/>
+            <a:off x="2605028" y="1840400"/>
+            <a:ext cx="899515" cy="2741463"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6566,10 +7052,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="88" name="Rectangle 37">
+          <xdr:cNvPr id="24" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C172EBC5-7274-4FE8-91B3-931A8AB32736}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6579,8 +7065,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="339725" y="2102668"/>
-            <a:ext cx="1149349" cy="240482"/>
+            <a:off x="296008" y="2590380"/>
+            <a:ext cx="1247711" cy="232060"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6716,28 +7202,15 @@
               </a:rPr>
               <a:t>一般ユーザグループ</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>1</a:t>
-            </a:r>
-            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="96" name="Rectangle 37">
+          <xdr:cNvPr id="25" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030735C4-9295-4139-A2BF-3685BFD3EF53}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6747,8 +7220,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5705259" y="5593996"/>
-            <a:ext cx="1400391" cy="425804"/>
+            <a:off x="6005123" y="5365078"/>
+            <a:ext cx="1519867" cy="403995"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6897,10 +7370,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="97" name="Rectangle 37">
+          <xdr:cNvPr id="26" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE7A7956-8BF9-43FA-BF96-D7DF9B0F7B35}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6910,8 +7383,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="5735127" y="1796538"/>
-            <a:ext cx="1384252" cy="263530"/>
+            <a:off x="6033789" y="1799365"/>
+            <a:ext cx="1871962" cy="251799"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7068,10 +7541,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="101" name="フローチャート : 磁気ディスク 100">
+          <xdr:cNvPr id="32" name="正方形/長方形 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C25F9F6-86A9-49DD-8368-3AD75EDDB02A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7079,850 +7552,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5598997" y="2675698"/>
-            <a:ext cx="1802626" cy="1577690"/>
-          </a:xfrm>
-          <a:prstGeom prst="flowChartMagneticDisk">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="CC99FF"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="9900CC"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>　</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>     サーバ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="102" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="3794125" y="1828801"/>
-            <a:ext cx="1702902" cy="2895599"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="accent6">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="t" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>Application</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>サーバ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="103" name="正方形/長方形 102">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5702592" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>１</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="104" name="正方形/長方形 103">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6234426" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>２</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="105" name="正方形/長方形 104">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6797140" y="3472006"/>
-            <a:ext cx="508648" cy="644066"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>DB</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>ｲﾝｽﾀﾝｽ</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>３</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="106" name="正方形/長方形 105">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2484559" y="2174822"/>
-            <a:ext cx="671810" cy="336730"/>
+            <a:off x="2690242" y="2161018"/>
+            <a:ext cx="729086" cy="321528"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8059,10 +7690,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="107" name="正方形/長方形 106">
+          <xdr:cNvPr id="34" name="正方形/長方形 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C11DF84-AE30-4CDE-B061-50F9898BE506}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8070,8 +7701,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2484559" y="2603598"/>
-            <a:ext cx="671810" cy="336730"/>
+            <a:off x="2690242" y="2707291"/>
+            <a:ext cx="729086" cy="320934"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8208,10 +7839,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="108" name="正方形/長方形 107">
+          <xdr:cNvPr id="35" name="正方形/長方形 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7015A2C9-7DF8-431C-A80F-DC03CC2EFC1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8219,157 +7850,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2484559" y="3038960"/>
-            <a:ext cx="671810" cy="336730"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>WEB3</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="112" name="正方形/長方形 111">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3971436" y="2180706"/>
-            <a:ext cx="1386024" cy="336730"/>
+            <a:off x="4304096" y="2166568"/>
+            <a:ext cx="1504254" cy="321528"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8502,7 +7984,7 @@
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>WEB1</a:t>
+              <a:t>WEB</a:t>
             </a:r>
             <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
@@ -8514,10 +7996,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="113" name="正方形/長方形 112">
+          <xdr:cNvPr id="37" name="正方形/長方形 36">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D1C70F-7607-4906-805E-2499787D4B0E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8525,165 +8007,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3968218" y="2590885"/>
-            <a:ext cx="1389241" cy="336730"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent4"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent4"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>会員</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>WEB2</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="114" name="正方形/長方形 113">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3968218" y="3026245"/>
-            <a:ext cx="1389241" cy="336730"/>
+            <a:off x="4300599" y="2695298"/>
+            <a:ext cx="1507750" cy="320934"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8828,10 +8153,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="118" name="正方形/長方形 117">
+          <xdr:cNvPr id="38" name="正方形/長方形 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D14AECC-E9E0-4BAE-9AF3-0B03B5F51DB6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8839,8 +8164,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3971926" y="4288570"/>
-            <a:ext cx="1333587" cy="311396"/>
+            <a:off x="4286403" y="4270971"/>
+            <a:ext cx="1513505" cy="296945"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -8970,133 +8295,12 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="119" name="カギ線コネクタ 118">
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="42" name="正方形/長方形 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="118" idx="3"/>
-            <a:endCxn id="105" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="5305512" y="4116072"/>
-            <a:ext cx="1745951" cy="328196"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="120" name="直線コネクタ 119">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="103" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5956916" y="4116072"/>
-            <a:ext cx="1" cy="314656"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:headEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="121" name="直線コネクタ 120">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="104" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6488750" y="4116072"/>
-            <a:ext cx="1" cy="307509"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:headEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="123" name="正方形/長方形 122">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CB45709-F3E0-489E-A4D5-205A692230B5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9104,8 +8308,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2493381" y="3020247"/>
-            <a:ext cx="2872901" cy="366371"/>
+            <a:off x="2699830" y="2689641"/>
+            <a:ext cx="3118108" cy="357464"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9238,10 +8442,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="125" name="正方形/長方形 124">
+          <xdr:cNvPr id="44" name="正方形/長方形 43">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49F8FC2D-E023-489D-90E5-2AE22264B1C2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9249,155 +8453,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2498987" y="2596248"/>
-            <a:ext cx="2872901" cy="366371"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="38100">
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="127" name="正方形/長方形 126">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2483450" y="2172533"/>
-            <a:ext cx="2896720" cy="370922"/>
+            <a:off x="2689038" y="2158859"/>
+            <a:ext cx="3143993" cy="362266"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9530,71 +8587,28 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="128" name="カギ線コネクタ 127">
+          <xdr:cNvPr id="46" name="カギ線コネクタ 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36F2E2BD-0297-4F68-A03D-ACBADFE2D190}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:stCxn id="113" idx="3"/>
-            <a:endCxn id="104" idx="0"/>
+            <a:cxnSpLocks/>
+            <a:stCxn id="37" idx="3"/>
+            <a:endCxn id="27" idx="2"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5357459" y="2759251"/>
-            <a:ext cx="1131291" cy="712755"/>
+            <a:off x="5808349" y="2855766"/>
+            <a:ext cx="872337" cy="318898"/>
           </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="131" name="カギ線コネクタ 130">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="114" idx="3"/>
-            <a:endCxn id="105" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5357459" y="3194610"/>
-            <a:ext cx="1694005" cy="277396"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+            </a:avLst>
           </a:prstGeom>
           <a:ln>
             <a:solidFill>
@@ -9620,10 +8634,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="133" name="Rectangle 37">
+          <xdr:cNvPr id="47" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75F4A3F8-5B61-4630-977E-001643E152C3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9633,8 +8647,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4713604" y="6087908"/>
-            <a:ext cx="3550293" cy="408142"/>
+            <a:off x="5109643" y="5788706"/>
+            <a:ext cx="1938857" cy="387337"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9767,10 +8781,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="134" name="Rectangle 37">
+          <xdr:cNvPr id="48" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000086000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F4D7935-FE5E-4C8A-B50F-46F80CC81358}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9780,8 +8794,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="4117637" y="5589476"/>
-            <a:ext cx="1312619" cy="401749"/>
+            <a:off x="4124325" y="5379429"/>
+            <a:ext cx="1872860" cy="383786"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -9957,22 +8971,23 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="135" name="カギ線コネクタ 134">
+          <xdr:cNvPr id="49" name="カギ線コネクタ 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57A5271-5E5C-4113-8252-286F96F90F0E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:stCxn id="112" idx="3"/>
-            <a:endCxn id="103" idx="0"/>
+            <a:cxnSpLocks/>
+            <a:stCxn id="35" idx="3"/>
+            <a:endCxn id="27" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5357460" y="2349071"/>
-            <a:ext cx="599456" cy="1122935"/>
+            <a:off x="5808350" y="2327332"/>
+            <a:ext cx="1328376" cy="412507"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -10001,10 +9016,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="138" name="右矢印 137">
+          <xdr:cNvPr id="50" name="右矢印 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5839805-50E1-49A5-B03B-8B11FCD9D1B4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10012,8 +9027,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="3950322">
-            <a:off x="4609023" y="5322693"/>
-            <a:ext cx="1452817" cy="143007"/>
+            <a:off x="5107600" y="5160225"/>
+            <a:ext cx="1106754" cy="154906"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10156,10 +9171,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="146" name="Rectangle 37">
+          <xdr:cNvPr id="51" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED17BFF-1754-47E8-8F27-39145D3FBE8A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10169,8 +9184,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1316877" y="6087907"/>
-            <a:ext cx="2313138" cy="408142"/>
+            <a:off x="1422610" y="5788705"/>
+            <a:ext cx="2510786" cy="387337"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10303,10 +9318,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="147" name="Rectangle 37">
+          <xdr:cNvPr id="52" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93D2C61-DAF2-4DC1-A87E-A4A0B06576F0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10316,8 +9331,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1422400" y="5568177"/>
-            <a:ext cx="1190261" cy="369073"/>
+            <a:off x="1699073" y="5262918"/>
+            <a:ext cx="1292172" cy="351343"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10466,10 +9481,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="150" name="Rectangle 37">
+          <xdr:cNvPr id="53" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6FF2C5F-35B4-4353-9255-0844B41B2646}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10479,8 +9494,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="2822575" y="5718958"/>
-            <a:ext cx="1309446" cy="348467"/>
+            <a:off x="3237684" y="5646050"/>
+            <a:ext cx="1421536" cy="333533"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -10629,10 +9644,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="160" name="右矢印 159">
+          <xdr:cNvPr id="54" name="右矢印 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16CBE5C0-95F5-4756-B9CA-56A72D40B8FA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10640,8 +9655,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="14796441">
-            <a:off x="4809761" y="5266642"/>
-            <a:ext cx="1415738" cy="172607"/>
+            <a:off x="5292303" y="5099227"/>
+            <a:ext cx="1135784" cy="187751"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -10784,69 +9799,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="161" name="正方形/長方形 160">
+          <xdr:cNvPr id="56" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A1000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20043632">
-            <a:off x="2723540" y="2610380"/>
-            <a:ext cx="4392659" cy="1832455"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent6"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent6"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent6"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>SAMPLE</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="163" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A3000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A11520-2A1D-408F-B604-EBDCBC2B3CF3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10856,8 +9812,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="1155152" y="1313677"/>
-            <a:ext cx="1130484" cy="470673"/>
+            <a:off x="1247187" y="1339077"/>
+            <a:ext cx="1227209" cy="448792"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11014,21 +9970,22 @@
       </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="82" name="カギ線コネクタ 81">
+          <xdr:cNvPr id="57" name="カギ線コネクタ 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{019FE981-1798-40D0-B71D-7F37127A9BE6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:endCxn id="127" idx="1"/>
+            <a:stCxn id="80" idx="3"/>
+            <a:endCxn id="44" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1148939" y="1871546"/>
-            <a:ext cx="1334511" cy="484861"/>
+          <a:xfrm flipV="1">
+            <a:off x="1143552" y="2339992"/>
+            <a:ext cx="1545485" cy="49354"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -11057,68 +10014,21 @@
       </xdr:cxnSp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="89" name="カギ線コネクタ 88">
+          <xdr:cNvPr id="59" name="カギ線コネクタ 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA83CD41-C7AC-42F7-A548-6376105D6CB0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
-            <a:endCxn id="107" idx="1"/>
+            <a:endCxn id="42" idx="1"/>
           </xdr:cNvCxnSpPr>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="1196564" y="2770376"/>
-            <a:ext cx="1287995" cy="2870"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:tailEnd type="arrow"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="91" name="カギ線コネクタ 90">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:endCxn id="123" idx="1"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="1148939" y="3201845"/>
-            <a:ext cx="1344442" cy="523901"/>
+            <a:off x="1240435" y="2866563"/>
+            <a:ext cx="1459395" cy="494973"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -11147,10 +10057,10 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="テキスト ボックス 19">
+          <xdr:cNvPr id="60" name="テキスト ボックス 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DE58D3D-A137-4DD1-8E57-0A07A9ECDC45}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11158,8 +10068,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1431926" y="2387599"/>
-            <a:ext cx="714374" cy="177800"/>
+            <a:off x="1547635" y="2498950"/>
+            <a:ext cx="775341" cy="169316"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11205,10 +10115,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="117" name="テキスト ボックス 116">
+          <xdr:cNvPr id="61" name="テキスト ボックス 60">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CA41892-879D-41E3-B498-1339DA622C6D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11216,8 +10126,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1479550" y="3711574"/>
-            <a:ext cx="571500" cy="149226"/>
+            <a:off x="1599389" y="3398873"/>
+            <a:ext cx="620076" cy="142368"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11263,10 +10173,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="122" name="Rectangle 37">
+          <xdr:cNvPr id="63" name="Rectangle 37">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D25285-BAF2-4920-A0CA-FEF27D886B95}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11276,8 +10186,8 @@
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="387350" y="3007543"/>
-            <a:ext cx="1136649" cy="237307"/>
+            <a:off x="362434" y="3707388"/>
+            <a:ext cx="1347443" cy="225443"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11411,174 +10321,6 @@
                 <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
                 <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               </a:rPr>
-              <a:t>一般ユーザグループ</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>2</a:t>
-            </a:r>
-            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="124" name="Rectangle 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="387350" y="3975918"/>
-            <a:ext cx="1241425" cy="237307"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:lnRef>
-          <a:fillRef idx="2">
-            <a:schemeClr val="accent3"/>
-          </a:fillRef>
-          <a:effectRef idx="1">
-            <a:schemeClr val="accent3"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
-                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              </a:rPr>
               <a:t>管理者ユーザグループ</a:t>
             </a:r>
           </a:p>
@@ -11586,10 +10328,10 @@
       </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="126" name="グループ化 125">
+          <xdr:cNvPr id="64" name="グループ化 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8B8E4FF-6D30-49E1-9547-F2E1B09EF1CA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11597,18 +10339,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="7686675" y="1939924"/>
-            <a:ext cx="273050" cy="727076"/>
+            <a:off x="8336607" y="1936225"/>
+            <a:ext cx="296401" cy="693869"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="129" name="円/楕円 128">
+            <xdr:cNvPr id="65" name="円/楕円 128">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6466ED1-F3AB-76C1-35D3-55045E12BFB4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11657,16 +10399,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="130" name="直線コネクタ 129">
+            <xdr:cNvPr id="66" name="直線コネクタ 65">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1B94BE7-97A4-8333-3988-8A2DEFF2A221}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="129" idx="1"/>
-              <a:endCxn id="129" idx="5"/>
+              <a:stCxn id="65" idx="1"/>
+              <a:endCxn id="65" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -11696,16 +10438,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="132" name="直線コネクタ 131">
+            <xdr:cNvPr id="67" name="直線コネクタ 66">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E24BAC7-97F7-E99F-3E80-2F3809B0BD21}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="129" idx="7"/>
-              <a:endCxn id="129" idx="3"/>
+              <a:stCxn id="65" idx="7"/>
+              <a:endCxn id="65" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -11736,10 +10478,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="136" name="テキスト ボックス 135">
+          <xdr:cNvPr id="68" name="テキスト ボックス 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000088000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38C594BC-BF05-4ADA-B0F9-8720B3D32C0C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11747,8 +10489,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7537450" y="2416174"/>
-            <a:ext cx="587375" cy="149226"/>
+            <a:off x="8174769" y="2390276"/>
+            <a:ext cx="637657" cy="142368"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -11794,10 +10536,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="139" name="右矢印 138">
+          <xdr:cNvPr id="69" name="右矢印 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11FFCEC8-5787-4763-BE64-2EDE891F776B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11805,8 +10547,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5437948" y="2016126"/>
-            <a:ext cx="2683702" cy="230060"/>
+            <a:off x="5895818" y="2009719"/>
+            <a:ext cx="2913157" cy="218607"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -11945,10 +10687,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="143" name="テキスト ボックス 142">
+          <xdr:cNvPr id="70" name="テキスト ボックス 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362E1E1C-B77B-49B1-96D1-C2C02FB06230}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11956,8 +10698,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5683250" y="5181599"/>
-            <a:ext cx="593725" cy="149226"/>
+            <a:off x="6162067" y="5115741"/>
+            <a:ext cx="644559" cy="140744"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12003,10 +10745,10 @@
       </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="144" name="グループ化 143">
+          <xdr:cNvPr id="71" name="グループ化 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80835035-7B65-417B-84CD-024951B5177C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12014,18 +10756,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm rot="16200000">
-            <a:off x="3049588" y="4695823"/>
-            <a:ext cx="288925" cy="1289052"/>
+            <a:off x="3322404" y="4565177"/>
+            <a:ext cx="275750" cy="1398872"/>
             <a:chOff x="1762125" y="1781175"/>
             <a:chExt cx="295275" cy="1190625"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="145" name="円/楕円 144">
+            <xdr:cNvPr id="72" name="円/楕円 144">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{597E2665-565B-7AE6-EC25-ED6C93F31BD1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12074,16 +10816,16 @@
         </xdr:sp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="151" name="直線コネクタ 150">
+            <xdr:cNvPr id="73" name="直線コネクタ 72">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000097000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5D15FF-6461-4AAB-765E-D10C04E28C61}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="145" idx="1"/>
-              <a:endCxn id="145" idx="5"/>
+              <a:stCxn id="72" idx="1"/>
+              <a:endCxn id="72" idx="5"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -12113,16 +10855,16 @@
         </xdr:cxnSp>
         <xdr:cxnSp macro="">
           <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="152" name="直線コネクタ 151">
+            <xdr:cNvPr id="74" name="直線コネクタ 73">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000098000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15B3A1A1-C546-938E-D1C1-19C6C9271C46}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvCxnSpPr>
-              <a:stCxn id="145" idx="7"/>
-              <a:endCxn id="145" idx="3"/>
+              <a:stCxn id="72" idx="7"/>
+              <a:endCxn id="72" idx="3"/>
             </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
@@ -12153,10 +10895,10 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="153" name="テキスト ボックス 152">
+          <xdr:cNvPr id="75" name="テキスト ボックス 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE805A00-B58D-44DC-9E5C-8FFEA627E4BC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12164,8 +10906,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2279650" y="5079999"/>
-            <a:ext cx="571500" cy="149226"/>
+            <a:off x="2467892" y="5015814"/>
+            <a:ext cx="620077" cy="142367"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -12211,10 +10953,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="149" name="右矢印 148">
+          <xdr:cNvPr id="76" name="右矢印 148">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEC7A79-5E1A-4D58-B1CA-BC54B21B4FF2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12222,8 +10964,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="8439195">
-            <a:off x="2032898" y="5251880"/>
-            <a:ext cx="2088890" cy="175670"/>
+            <a:off x="2848194" y="5104877"/>
+            <a:ext cx="1635457" cy="166454"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -12366,10 +11108,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="148" name="右矢印 147">
+          <xdr:cNvPr id="77" name="右矢印 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000094000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B676FDB-9EF0-4187-B489-DD80EB189CF7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12377,8 +11119,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="19186654">
-            <a:off x="2478790" y="5288454"/>
-            <a:ext cx="1778315" cy="195155"/>
+            <a:off x="3235740" y="5095509"/>
+            <a:ext cx="1581989" cy="184831"/>
           </a:xfrm>
           <a:prstGeom prst="rightArrow">
             <a:avLst/>
@@ -12519,190 +11261,2038 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>88446</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>70553</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>33945</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="155" name="図 154" descr="çå£ãªé¡ã®ãã¬ãã©ã³ã»ãªãã¬ã¼ã¿ã¼ã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="78" name="図 77" descr="çå£ãªé¡ã®ãã¬ãã©ã³ã»ãªãã¬ã¼ã¿ã¼ã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BD0CDD3-9342-4CBD-90D0-DB15570F6313}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="589628" y="3156279"/>
+            <a:ext cx="534537" cy="535296"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
           <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
             </a:ext>
           </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="80" name="図 79" descr="ãã½ã³ã³ãä½¿ãã¹ãã¼ãã¦ã§ã¢ãçãäººã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16FB49CB-C51D-4BAE-8803-25D247313989}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="609016" y="2116992"/>
+            <a:ext cx="534537" cy="542710"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
           <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
             </a:ext>
           </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="646339" y="3336254"/>
-          <a:ext cx="540000" cy="534905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="83" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99C1AEB1-9A50-43F8-A71F-DBA396504E78}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="548943" y="4390289"/>
+            <a:ext cx="543548" cy="1661181"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="eaVert" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>接続先システム</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>4</a:t>
+            </a:r>
+            <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>136071</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>74839</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>118178</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>41035</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="165" name="図 164" descr="ãã½ã³ã³ãä½¿ãå¥³æ§ã®ã¤ã©ã¹ã">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="693964" y="2483303"/>
-          <a:ext cx="540000" cy="537696"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="84" name="グループ化 83">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45CEB5C7-FDAD-4F9B-9732-3CEC616D109B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1762505" y="4569737"/>
+            <a:ext cx="296402" cy="693869"/>
+            <a:chOff x="1762125" y="1781175"/>
+            <a:chExt cx="295275" cy="1190625"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="90" name="円/楕円 128">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E16BD55-C069-9F25-8DB0-F8298B5BACA7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1762125" y="1781175"/>
+              <a:ext cx="295275" cy="1190625"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="92" name="直線コネクタ 91">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90FBA3E-DED3-421E-B02D-CB616CD20CB8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="90" idx="1"/>
+              <a:endCxn id="90" idx="5"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1805367" y="1955538"/>
+              <a:ext cx="208791" cy="841899"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="93" name="直線コネクタ 92">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637E3562-31A2-C61F-3843-F27B0C826E71}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="90" idx="7"/>
+              <a:endCxn id="90" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="1805367" y="1955538"/>
+              <a:ext cx="208791" cy="841899"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="94" name="テキスト ボックス 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4FCE84-C8AA-4B4F-B682-3498613BE4DA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1600669" y="5053921"/>
+            <a:ext cx="637328" cy="142368"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>専用線</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="95" name="正方形/長方形 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{170D624C-5DD1-4D59-892E-B48F6C666299}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2690242" y="3740028"/>
+            <a:ext cx="729086" cy="327056"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent4"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>WEB3</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="98" name="右矢印 138">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179CBB36-6CEA-42AB-8910-FC12EAFEA35D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="19086508">
+            <a:off x="977007" y="4700071"/>
+            <a:ext cx="1853161" cy="213285"/>
+          </a:xfrm>
+          <a:prstGeom prst="rightArrow">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="6350">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>122464</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>74838</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>104571</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>43724</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="166" name="図 165" descr="ãã½ã³ã³ãä½¿ãã¹ãã¼ãã¦ã§ã¢ãçãäººã®ã¤ã©ã¹ãï¼ç·æ§ï¼">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A6000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="680357" y="1626052"/>
-          <a:ext cx="540000" cy="540386"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="99" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4265B873-D8FF-40C8-B03B-E3788EF79099}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="1033097" y="4123127"/>
+            <a:ext cx="1500421" cy="456346"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>API</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>連携</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(HTTPS/REST)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="100" name="正方形/長方形 99">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0444AD42-E448-4A07-8F97-5FA6CFD1FE96}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4300599" y="3746868"/>
+            <a:ext cx="1507750" cy="327056"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent4"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent4"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>REST</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" baseline="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t> API</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="157" name="正方形/長方形 156">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED59415-4701-4061-9CB0-DED7AB58A1EB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2699830" y="3741211"/>
+            <a:ext cx="3118108" cy="347407"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="20" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACF4A30-4281-8864-61FC-B49D5B39294A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:stCxn id="157" idx="3"/>
+            <a:endCxn id="79" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="5817938" y="3596075"/>
+            <a:ext cx="1118751" cy="318840"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent5"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent5"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent5"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="36" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D0F8DF1-A7C8-D21C-5848-EE8C7076B946}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:endCxn id="45" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="5802289" y="3596074"/>
+            <a:ext cx="1561300" cy="757886"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="85" name="グループ化 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EB8EA20-3EBB-BE4C-FDF2-F1ABFB5B6BB3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="6680686" y="2739839"/>
+            <a:ext cx="912079" cy="869648"/>
+            <a:chOff x="6659617" y="2641708"/>
+            <a:chExt cx="910993" cy="879687"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="フローチャート : 磁気ディスク 100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B389504-078E-4CAD-9FC3-A8DB8780E41F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6659617" y="2641708"/>
+              <a:ext cx="910993" cy="879687"/>
+            </a:xfrm>
+            <a:prstGeom prst="flowChartMagneticDisk">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="CC99FF"/>
+            </a:solidFill>
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="9900CC"/>
               </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent3"/>
+            </a:lnRef>
+            <a:fillRef idx="2">
+              <a:schemeClr val="accent3"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent3"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="1"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                </a:rPr>
+                <a:t>DB</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                </a:rPr>
+                <a:t>サーバ</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="正方形/長方形 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31833AC4-B49C-8984-3086-35A9D98D0854}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7182835" y="3229303"/>
+              <a:ext cx="318924" cy="278525"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="79" name="正方形/長方形 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B623185-3A5E-FF23-B1A7-18FE56355B05}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6755853" y="3229303"/>
+              <a:ext cx="318924" cy="278525"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="55" name="正方形/長方形 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF57B4A-2B4A-40D8-9F51-0883CCC83BC6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="20043632">
+            <a:off x="2992039" y="2476443"/>
+            <a:ext cx="4768022" cy="1747786"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="9600">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>SAMPLE</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="9600">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C920392B-4601-B6A5-1373-D3B461274E36}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="6991350" y="4581524"/>
+            <a:ext cx="1076325" cy="276225"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>SMTP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1000" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>サーバー</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="3" name="カギ線コネクタ 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6FA7AE5-5EE5-DD09-446C-B5E61C2E4CC8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:endCxn id="2" idx="1"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5814851" y="4477250"/>
+            <a:ext cx="1176499" cy="242387"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:ln>
+            <a:tailEnd type="arrow"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="29" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F40A95B-9DA8-4CAB-8DBB-04B87B0F1E08}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="5677959" y="4689976"/>
+            <a:ext cx="1216017" cy="262432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:lnRef>
+          <a:fillRef idx="2">
+            <a:schemeClr val="accent3"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent3"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" anchor="ctr" anchorCtr="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>メール送信</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP" sz="900" b="0">
+                <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>(SMTP)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -13029,7 +13619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI423"/>
@@ -13045,131 +13635,131 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="1" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="1" t="s">
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="44"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="42"/>
+      <c r="AH1" s="42"/>
+      <c r="AI1" s="43"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="46"/>
       <c r="P2" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="57" t="s">
+      <c r="R2" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="62"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="58"/>
       <c r="Y3" s="11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="44"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="43"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13193,7 +13783,7 @@
     <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="14"/>
       <c r="D8" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13251,7 +13841,7 @@
     <row r="44" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="45" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D45" s="15" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13262,12 +13852,12 @@
         <v>2.2.</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D49" s="15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13302,13 +13892,13 @@
         <v>2.3.</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="14"/>
       <c r="D77" s="15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13318,7 +13908,7 @@
     </row>
     <row r="79" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D79" s="16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="3:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13333,7 +13923,7 @@
         <v>2.4.</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
@@ -13376,7 +13966,7 @@
         <v>2.4.1.</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18"/>
@@ -13452,7 +14042,7 @@
       <c r="C84" s="17"/>
       <c r="D84" s="19"/>
       <c r="E84" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="18"/>
@@ -13491,7 +14081,7 @@
       <c r="C85" s="17"/>
       <c r="D85" s="19"/>
       <c r="E85" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
@@ -13567,19 +14157,19 @@
       <c r="C87" s="17"/>
       <c r="D87" s="19"/>
       <c r="E87" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F87" s="21"/>
       <c r="G87" s="22"/>
       <c r="H87" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I87" s="21"/>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
       <c r="L87" s="22"/>
       <c r="M87" s="20" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="N87" s="21"/>
       <c r="O87" s="21"/>
@@ -13609,20 +14199,20 @@
       <c r="B88" s="18"/>
       <c r="C88" s="17"/>
       <c r="D88" s="19"/>
-      <c r="E88" s="32" t="s">
-        <v>23</v>
+      <c r="E88" s="31" t="s">
+        <v>28</v>
       </c>
-      <c r="F88" s="33"/>
-      <c r="G88" s="34"/>
-      <c r="H88" s="38" t="s">
-        <v>31</v>
+      <c r="F88" s="32"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="37" t="s">
+        <v>29</v>
       </c>
-      <c r="I88" s="33"/>
-      <c r="J88" s="33"/>
-      <c r="K88" s="33"/>
-      <c r="L88" s="34"/>
+      <c r="I88" s="32"/>
+      <c r="J88" s="32"/>
+      <c r="K88" s="32"/>
+      <c r="L88" s="33"/>
       <c r="M88" s="23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N88" s="24"/>
       <c r="O88" s="24"/>
@@ -13652,38 +14242,38 @@
       <c r="B89" s="18"/>
       <c r="C89" s="17"/>
       <c r="D89" s="19"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="40"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="40"/>
-      <c r="J89" s="40"/>
-      <c r="K89" s="40"/>
-      <c r="L89" s="41"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="40"/>
       <c r="M89" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
-      <c r="N89" s="27"/>
-      <c r="O89" s="27"/>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="27"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-      <c r="U89" s="27"/>
-      <c r="V89" s="27"/>
-      <c r="W89" s="27"/>
-      <c r="X89" s="27"/>
-      <c r="Y89" s="27"/>
-      <c r="Z89" s="27"/>
-      <c r="AA89" s="27"/>
-      <c r="AB89" s="27"/>
-      <c r="AC89" s="27"/>
-      <c r="AD89" s="27"/>
-      <c r="AE89" s="27"/>
-      <c r="AF89" s="27"/>
-      <c r="AG89" s="27"/>
-      <c r="AH89" s="28"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+      <c r="P89" s="18"/>
+      <c r="Q89" s="18"/>
+      <c r="R89" s="18"/>
+      <c r="S89" s="18"/>
+      <c r="T89" s="18"/>
+      <c r="U89" s="18"/>
+      <c r="V89" s="18"/>
+      <c r="W89" s="18"/>
+      <c r="X89" s="18"/>
+      <c r="Y89" s="18"/>
+      <c r="Z89" s="18"/>
+      <c r="AA89" s="18"/>
+      <c r="AB89" s="18"/>
+      <c r="AC89" s="18"/>
+      <c r="AD89" s="18"/>
+      <c r="AE89" s="18"/>
+      <c r="AF89" s="18"/>
+      <c r="AG89" s="18"/>
+      <c r="AH89" s="27"/>
       <c r="AI89" s="18"/>
     </row>
     <row r="90" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -13691,20 +14281,20 @@
       <c r="B90" s="18"/>
       <c r="C90" s="17"/>
       <c r="D90" s="19"/>
-      <c r="E90" s="32" t="s">
-        <v>25</v>
+      <c r="E90" s="31" t="s">
+        <v>32</v>
       </c>
-      <c r="F90" s="33"/>
-      <c r="G90" s="34"/>
-      <c r="H90" s="32" t="s">
+      <c r="F90" s="32"/>
+      <c r="G90" s="33"/>
+      <c r="H90" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I90" s="32"/>
+      <c r="J90" s="32"/>
+      <c r="K90" s="32"/>
+      <c r="L90" s="33"/>
+      <c r="M90" s="23" t="s">
         <v>34</v>
-      </c>
-      <c r="I90" s="33"/>
-      <c r="J90" s="33"/>
-      <c r="K90" s="33"/>
-      <c r="L90" s="34"/>
-      <c r="M90" s="23" t="s">
-        <v>33</v>
       </c>
       <c r="N90" s="24"/>
       <c r="O90" s="24"/>
@@ -13734,36 +14324,36 @@
       <c r="B91" s="18"/>
       <c r="C91" s="17"/>
       <c r="D91" s="19"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="36"/>
-      <c r="J91" s="36"/>
-      <c r="K91" s="36"/>
-      <c r="L91" s="37"/>
-      <c r="M91" s="29"/>
-      <c r="N91" s="30"/>
-      <c r="O91" s="30"/>
-      <c r="P91" s="30"/>
-      <c r="Q91" s="30"/>
-      <c r="R91" s="30"/>
-      <c r="S91" s="30"/>
-      <c r="T91" s="30"/>
-      <c r="U91" s="30"/>
-      <c r="V91" s="30"/>
-      <c r="W91" s="30"/>
-      <c r="X91" s="30"/>
-      <c r="Y91" s="30"/>
-      <c r="Z91" s="30"/>
-      <c r="AA91" s="30"/>
-      <c r="AB91" s="30"/>
-      <c r="AC91" s="30"/>
-      <c r="AD91" s="30"/>
-      <c r="AE91" s="30"/>
-      <c r="AF91" s="30"/>
-      <c r="AG91" s="30"/>
-      <c r="AH91" s="31"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="34"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="35"/>
+      <c r="L91" s="36"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="29"/>
+      <c r="O91" s="29"/>
+      <c r="P91" s="29"/>
+      <c r="Q91" s="29"/>
+      <c r="R91" s="29"/>
+      <c r="S91" s="29"/>
+      <c r="T91" s="29"/>
+      <c r="U91" s="29"/>
+      <c r="V91" s="29"/>
+      <c r="W91" s="29"/>
+      <c r="X91" s="29"/>
+      <c r="Y91" s="29"/>
+      <c r="Z91" s="29"/>
+      <c r="AA91" s="29"/>
+      <c r="AB91" s="29"/>
+      <c r="AC91" s="29"/>
+      <c r="AD91" s="29"/>
+      <c r="AE91" s="29"/>
+      <c r="AF91" s="29"/>
+      <c r="AG91" s="29"/>
+      <c r="AH91" s="30"/>
       <c r="AI91" s="18"/>
     </row>
     <row r="92" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -14154,7 +14744,7 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="D79" r:id="rId1" display="https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/nablarch/big_picture.html" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D79" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId2"/>
